--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joeyaj/Desktop/Woosong-Apply/Woosong-Apply/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453075A6-63FD-3C42-BAD7-4591D02EFF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D935673F-F302-9141-8287-AAF11D591E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1240" yWindow="660" windowWidth="29000" windowHeight="14040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1240" yWindow="660" windowWidth="29000" windowHeight="14040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Claude Log" sheetId="5" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="102">
   <si>
     <t>又松大学招生系统 - 使用说明</t>
   </si>
@@ -1240,9 +1240,15 @@
     </row>
     <row r="6" spans="1:17" ht="48" customHeight="1">
       <c r="A6" s="6"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+      <c r="B6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="22">
+        <v>46178</v>
+      </c>
       <c r="E6" s="7" t="s">
         <v>47</v>
       </c>
@@ -1283,9 +1289,15 @@
     </row>
     <row r="7" spans="1:17" ht="48" customHeight="1">
       <c r="A7" s="9"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
+      <c r="B7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="22">
+        <v>46178</v>
+      </c>
       <c r="E7" s="7" t="s">
         <v>43</v>
       </c>
@@ -1326,9 +1338,15 @@
     </row>
     <row r="8" spans="1:17" ht="48" customHeight="1">
       <c r="A8" s="9"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+      <c r="B8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="22">
+        <v>46178</v>
+      </c>
       <c r="E8" s="7" t="s">
         <v>54</v>
       </c>
@@ -1369,9 +1387,15 @@
     </row>
     <row r="9" spans="1:17" ht="48" customHeight="1">
       <c r="A9" s="9"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
+      <c r="B9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="22">
+        <v>46178</v>
+      </c>
       <c r="E9" s="7" t="s">
         <v>59</v>
       </c>
@@ -1412,9 +1436,15 @@
     </row>
     <row r="10" spans="1:17" ht="48" customHeight="1">
       <c r="A10" s="9"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="B10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="22">
+        <v>46178</v>
+      </c>
       <c r="E10" s="7" t="s">
         <v>50</v>
       </c>
@@ -1455,9 +1485,15 @@
     </row>
     <row r="11" spans="1:17" ht="48" customHeight="1">
       <c r="A11" s="9"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
+      <c r="B11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="22">
+        <v>46178</v>
+      </c>
       <c r="E11" s="7" t="s">
         <v>57</v>
       </c>
@@ -1498,9 +1534,15 @@
     </row>
     <row r="12" spans="1:17" ht="48" customHeight="1">
       <c r="A12" s="9"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
+      <c r="B12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="22">
+        <v>46178</v>
+      </c>
       <c r="E12" s="7" t="s">
         <v>56</v>
       </c>
@@ -1541,9 +1583,15 @@
     </row>
     <row r="13" spans="1:17" ht="48" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
+      <c r="B13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="22">
+        <v>46178</v>
+      </c>
       <c r="E13" s="7" t="s">
         <v>56</v>
       </c>
@@ -1584,9 +1632,15 @@
     </row>
     <row r="14" spans="1:17" ht="48" customHeight="1">
       <c r="A14" s="10"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
+      <c r="B14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="22">
+        <v>46178</v>
+      </c>
       <c r="E14" s="11" t="s">
         <v>50</v>
       </c>
@@ -1627,9 +1681,15 @@
     </row>
     <row r="15" spans="1:17" ht="28">
       <c r="A15" s="10"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
+      <c r="B15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="22">
+        <v>46178</v>
+      </c>
       <c r="E15" s="11" t="s">
         <v>80</v>
       </c>
@@ -1670,9 +1730,15 @@
     </row>
     <row r="16" spans="1:17" ht="28">
       <c r="A16" s="10"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="22">
+        <v>46178</v>
+      </c>
       <c r="E16" s="11" t="s">
         <v>53</v>
       </c>
@@ -1713,9 +1779,15 @@
     </row>
     <row r="17" spans="1:17" ht="28">
       <c r="A17" s="10"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
+      <c r="B17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="22">
+        <v>46178</v>
+      </c>
       <c r="E17" s="11" t="s">
         <v>53</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joeyaj/Desktop/Woosong-Apply/Woosong-Apply/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D935673F-F302-9141-8287-AAF11D591E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062C3298-1587-BC4D-BA77-26A87DE1D6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1240" yWindow="660" windowWidth="29000" windowHeight="14040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1240" yWindow="660" windowWidth="29000" windowHeight="14040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Claude Log" sheetId="5" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="105">
   <si>
     <t>又松大学招生系统 - 使用说明</t>
   </si>
@@ -115,9 +115,6 @@
   </si>
   <si>
     <t>授课语言</t>
-  </si>
-  <si>
-    <t>询问</t>
   </si>
   <si>
     <t>申请</t>
@@ -269,9 +266,6 @@
     <t>경영 전공</t>
   </si>
   <si>
-    <t>询问数未在动态表中统计；面试按动态表中面试时间非空人数统计；入学暂无来源，暂按0。</t>
-  </si>
-  <si>
     <t>AI경영 전공</t>
   </si>
   <si>
@@ -287,12 +281,6 @@
     <t>철도경영학과</t>
   </si>
   <si>
-    <t>询问数未在动态表中统计；源表无面试时间列，面试暂按0；入学按学号/入境状态非空统计（现均为空）。</t>
-  </si>
-  <si>
-    <t>询问数未在动态表中统计；源表无面试时间列，面试暂按0；入学暂无来源，暂按0。</t>
-  </si>
-  <si>
     <t>Turn #</t>
   </si>
   <si>
@@ -345,6 +333,28 @@
   </si>
   <si>
     <t>【大学院】周报月报 H列已填，4组语言均无混合。</t>
+  </si>
+  <si>
+    <t>取消</t>
+  </si>
+  <si>
+    <t>询问数未在动态表中统计；面试按面试时间非空人数统计；取消无来源暂按0；入学=申请−取消。</t>
+  </si>
+  <si>
+    <t>询问数未在动态表中统计；源表无面试时间列，面试暂按0；取消无来源暂按0；入学=申请−取消。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>三张表在标入后增加取消列，入学=申请-取消。</t>
+  </si>
+  <si>
+    <t>新增取消列并将入学改为公式</t>
+  </si>
+  <si>
+    <t>学部取消=P入学=Q(=J-P)备注R；大学院取消=P入学=Q(=J-P)备注R；SolBridge取消=N入学=O(=H-N)备注P。源表无取消数据，取消暂为0故入学=申请。</t>
+  </si>
+  <si>
+    <t>三表入学列已改为动态公式，随取消列自动重算。</t>
   </si>
 </sst>
 </file>
@@ -445,7 +455,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -466,13 +476,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -565,7 +568,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -586,25 +589,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -627,7 +627,7 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -847,87 +847,107 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738CB936-C75A-7447-9910-9C93B26D3435}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="F1" s="25" t="s">
         <v>85</v>
-      </c>
-      <c r="C1" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="D1" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="26">
         <v>46178</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="26">
         <v>46178</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="26">
         <v>46178</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="26">
+        <v>46178</v>
+      </c>
+      <c r="C5" t="s">
         <v>101</v>
+      </c>
+      <c r="D5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -945,12 +965,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
@@ -1018,8 +1038,8 @@
       </c>
     </row>
     <row r="20" spans="1:1" ht="15">
-      <c r="A20" s="23" t="s">
-        <v>74</v>
+      <c r="A20" s="22" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1063,77 +1083,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="20">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
     </row>
     <row r="3" spans="1:17" ht="42.75" customHeight="1">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="L3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="M3" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="N3" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="O3" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="P3" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="Q3" s="13" t="s">
         <v>33</v>
-      </c>
-      <c r="Q3" s="14" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="48" customHeight="1">
@@ -1141,50 +1161,53 @@
         <v>2026</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="24">
+        <v>41</v>
+      </c>
+      <c r="D4" s="23">
         <v>46178</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" s="4"/>
+      <c r="I4" s="4">
+        <v>4</v>
+      </c>
       <c r="J4" s="4">
         <v>4</v>
       </c>
       <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <f>I4-O4</f>
         <v>4</v>
       </c>
-      <c r="L4" s="4">
-        <v>0</v>
-      </c>
-      <c r="M4" s="4">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4">
-        <v>0</v>
-      </c>
-      <c r="O4" s="4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4">
-        <v>0</v>
-      </c>
       <c r="Q4" s="5" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="48" customHeight="1">
@@ -1192,638 +1215,677 @@
         <v>2026</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="22">
+        <v>41</v>
+      </c>
+      <c r="D5" s="21">
         <v>46178</v>
       </c>
       <c r="E5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>49</v>
-      </c>
       <c r="H5" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1</v>
+      </c>
       <c r="J5" s="7">
+        <v>0</v>
+      </c>
+      <c r="K5" s="7">
         <v>1</v>
       </c>
-      <c r="K5" s="7">
-        <v>0</v>
-      </c>
       <c r="L5" s="7">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7">
+        <v>0</v>
+      </c>
+      <c r="N5" s="7">
+        <v>0</v>
+      </c>
+      <c r="O5" s="7">
+        <v>0</v>
+      </c>
+      <c r="P5" s="7">
+        <f>I5-O5</f>
         <v>1</v>
       </c>
-      <c r="M5" s="7">
-        <v>0</v>
-      </c>
-      <c r="N5" s="7">
-        <v>0</v>
-      </c>
-      <c r="O5" s="7">
-        <v>0</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>76</v>
+      <c r="Q5" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="48" customHeight="1">
       <c r="A6" s="6"/>
       <c r="B6" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="21">
+        <v>46178</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="7">
+        <v>3</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7">
+        <v>0</v>
+      </c>
+      <c r="M6" s="7">
+        <v>0</v>
+      </c>
+      <c r="N6" s="7">
+        <v>0</v>
+      </c>
+      <c r="O6" s="7">
+        <v>0</v>
+      </c>
+      <c r="P6" s="7">
+        <f>I6-O6</f>
+        <v>3</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="48" customHeight="1">
+      <c r="A7" s="8"/>
+      <c r="B7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="21">
+        <v>46178</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="22">
+      <c r="F7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" s="7">
+        <v>4</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="7">
+        <v>0</v>
+      </c>
+      <c r="L7" s="7">
+        <v>0</v>
+      </c>
+      <c r="M7" s="7">
+        <v>0</v>
+      </c>
+      <c r="N7" s="7">
+        <v>0</v>
+      </c>
+      <c r="O7" s="7">
+        <v>0</v>
+      </c>
+      <c r="P7" s="7">
+        <f>I7-O7</f>
+        <v>4</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="48" customHeight="1">
+      <c r="A8" s="8"/>
+      <c r="B8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="21">
         <v>46178</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7">
-        <v>3</v>
-      </c>
-      <c r="K6" s="7">
-        <v>0</v>
-      </c>
-      <c r="L6" s="7">
-        <v>0</v>
-      </c>
-      <c r="M6" s="7">
-        <v>0</v>
-      </c>
-      <c r="N6" s="7">
-        <v>0</v>
-      </c>
-      <c r="O6" s="7">
-        <v>0</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="48" customHeight="1">
-      <c r="A7" s="9"/>
-      <c r="B7" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="22">
+      <c r="E8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="I8" s="7">
+        <v>1</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7">
+        <v>0</v>
+      </c>
+      <c r="L8" s="7">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7">
+        <v>0</v>
+      </c>
+      <c r="N8" s="7">
+        <v>0</v>
+      </c>
+      <c r="O8" s="7">
+        <v>0</v>
+      </c>
+      <c r="P8" s="7">
+        <f>I8-O8</f>
+        <v>1</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="48" customHeight="1">
+      <c r="A9" s="8"/>
+      <c r="B9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="21">
         <v>46178</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7">
-        <v>4</v>
-      </c>
-      <c r="K7" s="7">
-        <v>0</v>
-      </c>
-      <c r="L7" s="7">
-        <v>0</v>
-      </c>
-      <c r="M7" s="7">
-        <v>0</v>
-      </c>
-      <c r="N7" s="7">
-        <v>0</v>
-      </c>
-      <c r="O7" s="7">
-        <v>0</v>
-      </c>
-      <c r="P7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="48" customHeight="1">
-      <c r="A8" s="9"/>
-      <c r="B8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="22">
-        <v>46178</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7">
+      <c r="E9" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="7">
         <v>1</v>
       </c>
-      <c r="K8" s="7">
-        <v>0</v>
-      </c>
-      <c r="L8" s="7">
-        <v>0</v>
-      </c>
-      <c r="M8" s="7">
-        <v>0</v>
-      </c>
-      <c r="N8" s="7">
-        <v>0</v>
-      </c>
-      <c r="O8" s="7">
-        <v>0</v>
-      </c>
-      <c r="P8" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1">
-      <c r="A9" s="9"/>
-      <c r="B9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="22">
-        <v>46178</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="I9" s="7"/>
       <c r="J9" s="7">
         <v>1</v>
       </c>
       <c r="K9" s="7">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7">
+        <v>0</v>
+      </c>
+      <c r="N9" s="7">
+        <v>0</v>
+      </c>
+      <c r="O9" s="7">
+        <v>0</v>
+      </c>
+      <c r="P9" s="7">
+        <f>I9-O9</f>
         <v>1</v>
       </c>
-      <c r="L9" s="7">
-        <v>0</v>
-      </c>
-      <c r="M9" s="7">
-        <v>0</v>
-      </c>
-      <c r="N9" s="7">
-        <v>0</v>
-      </c>
-      <c r="O9" s="7">
-        <v>0</v>
-      </c>
-      <c r="P9" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="8" t="s">
-        <v>76</v>
+      <c r="Q9" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="48" customHeight="1">
-      <c r="A10" s="9"/>
+      <c r="A10" s="8"/>
       <c r="B10" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="22">
+        <v>41</v>
+      </c>
+      <c r="D10" s="21">
         <v>46178</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10" s="7"/>
+      <c r="I10" s="7">
+        <v>1</v>
+      </c>
       <c r="J10" s="7">
         <v>1</v>
       </c>
       <c r="K10" s="7">
+        <v>0</v>
+      </c>
+      <c r="L10" s="7">
+        <v>0</v>
+      </c>
+      <c r="M10" s="7">
+        <v>0</v>
+      </c>
+      <c r="N10" s="7">
+        <v>0</v>
+      </c>
+      <c r="O10" s="7">
+        <v>0</v>
+      </c>
+      <c r="P10" s="7">
+        <f>I10-O10</f>
         <v>1</v>
       </c>
-      <c r="L10" s="7">
-        <v>0</v>
-      </c>
-      <c r="M10" s="7">
-        <v>0</v>
-      </c>
-      <c r="N10" s="7">
-        <v>0</v>
-      </c>
-      <c r="O10" s="7">
-        <v>0</v>
-      </c>
-      <c r="P10" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="8" t="s">
-        <v>76</v>
+      <c r="Q10" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="48" customHeight="1">
-      <c r="A11" s="9"/>
+      <c r="A11" s="8"/>
       <c r="B11" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="22">
+        <v>41</v>
+      </c>
+      <c r="D11" s="21">
         <v>46178</v>
       </c>
       <c r="E11" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="G11" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="I11" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="I11" s="7">
+        <v>1</v>
+      </c>
       <c r="J11" s="7">
         <v>1</v>
       </c>
       <c r="K11" s="7">
+        <v>0</v>
+      </c>
+      <c r="L11" s="7">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7">
+        <v>0</v>
+      </c>
+      <c r="N11" s="7">
+        <v>0</v>
+      </c>
+      <c r="O11" s="7">
+        <v>0</v>
+      </c>
+      <c r="P11" s="7">
+        <f>I11-O11</f>
         <v>1</v>
       </c>
-      <c r="L11" s="7">
-        <v>0</v>
-      </c>
-      <c r="M11" s="7">
-        <v>0</v>
-      </c>
-      <c r="N11" s="7">
-        <v>0</v>
-      </c>
-      <c r="O11" s="7">
-        <v>0</v>
-      </c>
-      <c r="P11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="8" t="s">
+      <c r="Q11" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="48" customHeight="1">
+      <c r="A12" s="8"/>
+      <c r="B12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="21">
+        <v>46178</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" ht="48" customHeight="1">
-      <c r="A12" s="9"/>
-      <c r="B12" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="22">
-        <v>46178</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>52</v>
+      <c r="G12" s="15" t="s">
+        <v>51</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I12" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="I12" s="7">
+        <v>1</v>
+      </c>
       <c r="J12" s="7">
         <v>1</v>
       </c>
       <c r="K12" s="7">
+        <v>0</v>
+      </c>
+      <c r="L12" s="7">
+        <v>0</v>
+      </c>
+      <c r="M12" s="7">
+        <v>0</v>
+      </c>
+      <c r="N12" s="7">
+        <v>0</v>
+      </c>
+      <c r="O12" s="7">
+        <v>0</v>
+      </c>
+      <c r="P12" s="7">
+        <f>I12-O12</f>
         <v>1</v>
       </c>
-      <c r="L12" s="7">
-        <v>0</v>
-      </c>
-      <c r="M12" s="7">
-        <v>0</v>
-      </c>
-      <c r="N12" s="7">
-        <v>0</v>
-      </c>
-      <c r="O12" s="7">
-        <v>0</v>
-      </c>
-      <c r="P12" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="8" t="s">
+      <c r="Q12" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="48" customHeight="1">
+      <c r="A13" s="8"/>
+      <c r="B13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="21">
+        <v>46178</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" ht="48" customHeight="1">
-      <c r="A13" s="9"/>
-      <c r="B13" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="22">
+      <c r="G13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="7">
+        <v>1</v>
+      </c>
+      <c r="J13" s="7">
+        <v>0</v>
+      </c>
+      <c r="K13" s="7">
+        <v>0</v>
+      </c>
+      <c r="L13" s="7">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7">
+        <v>0</v>
+      </c>
+      <c r="N13" s="7">
+        <v>0</v>
+      </c>
+      <c r="O13" s="7">
+        <v>0</v>
+      </c>
+      <c r="P13" s="7">
+        <f>I13-O13</f>
+        <v>1</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="48" customHeight="1">
+      <c r="A14" s="9"/>
+      <c r="B14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="21">
         <v>46178</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="7" t="s">
+      <c r="E14" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I14" s="10">
+        <v>3</v>
+      </c>
+      <c r="J14" s="10">
+        <v>3</v>
+      </c>
+      <c r="K14" s="10">
+        <v>0</v>
+      </c>
+      <c r="L14" s="10">
+        <v>0</v>
+      </c>
+      <c r="M14" s="10">
+        <v>0</v>
+      </c>
+      <c r="N14" s="10">
+        <v>0</v>
+      </c>
+      <c r="O14" s="10">
+        <v>0</v>
+      </c>
+      <c r="P14" s="10">
+        <f>I14-O14</f>
+        <v>3</v>
+      </c>
+      <c r="Q14" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="42">
+      <c r="A15" s="9"/>
+      <c r="B15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="21">
+        <v>46178</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7">
+      <c r="F15" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15" s="10">
         <v>1</v>
       </c>
-      <c r="K13" s="7">
-        <v>0</v>
-      </c>
-      <c r="L13" s="7">
-        <v>0</v>
-      </c>
-      <c r="M13" s="7">
-        <v>0</v>
-      </c>
-      <c r="N13" s="7">
-        <v>0</v>
-      </c>
-      <c r="O13" s="7">
-        <v>0</v>
-      </c>
-      <c r="P13" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="48" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="22">
+      <c r="J15" s="10">
+        <v>0</v>
+      </c>
+      <c r="K15" s="10">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10">
+        <v>0</v>
+      </c>
+      <c r="M15" s="10">
+        <v>0</v>
+      </c>
+      <c r="N15" s="10">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10">
+        <v>0</v>
+      </c>
+      <c r="P15" s="10">
+        <f>I15-O15</f>
+        <v>1</v>
+      </c>
+      <c r="Q15" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="42">
+      <c r="A16" s="9"/>
+      <c r="B16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="21">
         <v>46178</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="H14" s="11" t="s">
+      <c r="E16" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11">
+      <c r="H16" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="10">
         <v>3</v>
       </c>
-      <c r="K14" s="11">
+      <c r="J16" s="10">
+        <v>0</v>
+      </c>
+      <c r="K16" s="10">
+        <v>0</v>
+      </c>
+      <c r="L16" s="10">
+        <v>0</v>
+      </c>
+      <c r="M16" s="10">
+        <v>0</v>
+      </c>
+      <c r="N16" s="10">
+        <v>0</v>
+      </c>
+      <c r="O16" s="10">
+        <v>0</v>
+      </c>
+      <c r="P16" s="10">
+        <f>I16-O16</f>
         <v>3</v>
       </c>
-      <c r="L14" s="11">
-        <v>0</v>
-      </c>
-      <c r="M14" s="11">
-        <v>0</v>
-      </c>
-      <c r="N14" s="11">
-        <v>0</v>
-      </c>
-      <c r="O14" s="11">
-        <v>0</v>
-      </c>
-      <c r="P14" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="28">
-      <c r="A15" s="10"/>
-      <c r="B15" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="22">
+      <c r="Q16" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="42">
+      <c r="A17" s="9"/>
+      <c r="B17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="21">
         <v>46178</v>
       </c>
-      <c r="E15" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="G15" s="11" t="s">
+      <c r="E17" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H15" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11">
-        <v>1</v>
-      </c>
-      <c r="K15" s="11">
-        <v>0</v>
-      </c>
-      <c r="L15" s="11">
-        <v>0</v>
-      </c>
-      <c r="M15" s="11">
-        <v>0</v>
-      </c>
-      <c r="N15" s="11">
-        <v>0</v>
-      </c>
-      <c r="O15" s="11">
-        <v>0</v>
-      </c>
-      <c r="P15" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="28">
-      <c r="A16" s="10"/>
-      <c r="B16" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="22">
-        <v>46178</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="11" t="s">
+      <c r="F17" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11">
-        <v>3</v>
-      </c>
-      <c r="K16" s="11">
-        <v>0</v>
-      </c>
-      <c r="L16" s="11">
-        <v>0</v>
-      </c>
-      <c r="M16" s="11">
-        <v>0</v>
-      </c>
-      <c r="N16" s="11">
-        <v>0</v>
-      </c>
-      <c r="O16" s="11">
-        <v>0</v>
-      </c>
-      <c r="P16" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="28">
-      <c r="A17" s="10"/>
-      <c r="B17" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="22">
-        <v>46178</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11">
+      <c r="G17" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17" s="10">
         <v>2</v>
       </c>
-      <c r="K17" s="11">
-        <v>0</v>
-      </c>
-      <c r="L17" s="11">
-        <v>0</v>
-      </c>
-      <c r="M17" s="11">
-        <v>0</v>
-      </c>
-      <c r="N17" s="11">
-        <v>0</v>
-      </c>
-      <c r="O17" s="11">
-        <v>0</v>
-      </c>
-      <c r="P17" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="8" t="s">
-        <v>76</v>
+      <c r="J17" s="10">
+        <v>0</v>
+      </c>
+      <c r="K17" s="10">
+        <v>0</v>
+      </c>
+      <c r="L17" s="10">
+        <v>0</v>
+      </c>
+      <c r="M17" s="10">
+        <v>0</v>
+      </c>
+      <c r="N17" s="10">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10">
+        <v>0</v>
+      </c>
+      <c r="P17" s="10">
+        <f>I17-O17</f>
+        <v>2</v>
+      </c>
+      <c r="Q17" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -2460,281 +2522,293 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="20">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+    </row>
+    <row r="3" spans="1:17" ht="42.75" customHeight="1">
+      <c r="A3" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-    </row>
-    <row r="3" spans="1:17" ht="42.75" customHeight="1">
-      <c r="A3" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="13" t="s">
+      <c r="G3" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="L3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="M3" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="N3" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="O3" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="P3" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="Q3" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="14" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="4" spans="1:17" ht="48" customHeight="1">
-      <c r="A4" s="15" t="s">
-        <v>40</v>
+      <c r="A4" s="14" t="s">
+        <v>39</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="22">
+        <v>41</v>
+      </c>
+      <c r="D4" s="21">
         <v>46178</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="4">
+        <v>3</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <f>I4-O4</f>
+        <v>3</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="48" customHeight="1">
+      <c r="A5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="21">
+        <v>46178</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4">
-        <v>3</v>
-      </c>
-      <c r="K4" s="4">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4">
-        <v>0</v>
-      </c>
-      <c r="M4" s="4">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4">
-        <v>0</v>
-      </c>
-      <c r="O4" s="4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="48" customHeight="1">
-      <c r="A5" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="22">
+      <c r="F5" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0</v>
+      </c>
+      <c r="K5" s="7">
+        <v>0</v>
+      </c>
+      <c r="L5" s="7">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7">
+        <v>0</v>
+      </c>
+      <c r="N5" s="7">
+        <v>0</v>
+      </c>
+      <c r="O5" s="7">
+        <v>0</v>
+      </c>
+      <c r="P5" s="7">
+        <f>I5-O5</f>
+        <v>1</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="48" customHeight="1">
+      <c r="A6" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="21">
         <v>46178</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="E6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7">
+      <c r="G6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="7">
         <v>1</v>
       </c>
-      <c r="K5" s="7">
-        <v>0</v>
-      </c>
-      <c r="L5" s="7">
-        <v>0</v>
-      </c>
-      <c r="M5" s="7">
-        <v>0</v>
-      </c>
-      <c r="N5" s="7">
-        <v>0</v>
-      </c>
-      <c r="O5" s="7">
-        <v>0</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="48" customHeight="1">
-      <c r="A6" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="22">
+      <c r="J6" s="7">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7">
+        <v>0</v>
+      </c>
+      <c r="M6" s="7">
+        <v>0</v>
+      </c>
+      <c r="N6" s="7">
+        <v>0</v>
+      </c>
+      <c r="O6" s="7">
+        <v>0</v>
+      </c>
+      <c r="P6" s="7">
+        <f>I6-O6</f>
+        <v>1</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="48" customHeight="1">
+      <c r="A7" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="24">
         <v>46178</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" s="7" t="s">
+      <c r="E7" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7">
-        <v>1</v>
-      </c>
-      <c r="K6" s="7">
-        <v>0</v>
-      </c>
-      <c r="L6" s="7">
-        <v>0</v>
-      </c>
-      <c r="M6" s="7">
-        <v>0</v>
-      </c>
-      <c r="N6" s="7">
-        <v>0</v>
-      </c>
-      <c r="O6" s="7">
-        <v>0</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="48" customHeight="1">
-      <c r="A7" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="25">
-        <v>46178</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11">
+      <c r="G7" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="10">
         <v>7</v>
       </c>
-      <c r="K7" s="11">
-        <v>0</v>
-      </c>
-      <c r="L7" s="11">
-        <v>0</v>
-      </c>
-      <c r="M7" s="11">
-        <v>0</v>
-      </c>
-      <c r="N7" s="11">
-        <v>0</v>
-      </c>
-      <c r="O7" s="11">
-        <v>0</v>
-      </c>
-      <c r="P7" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>82</v>
+      <c r="J7" s="10">
+        <v>0</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10">
+        <v>0</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0</v>
+      </c>
+      <c r="N7" s="10">
+        <v>0</v>
+      </c>
+      <c r="O7" s="10">
+        <v>0</v>
+      </c>
+      <c r="P7" s="10">
+        <f>I7-O7</f>
+        <v>7</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -3556,253 +3630,265 @@
     <col min="5" max="5" width="34" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="14" width="10" customWidth="1"/>
-    <col min="15" max="15" width="42" customWidth="1"/>
+    <col min="15" max="15" width="69.19921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+    </row>
+    <row r="3" spans="1:15" ht="42.75" customHeight="1">
+      <c r="A3" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-    </row>
-    <row r="3" spans="1:15" ht="42.75" customHeight="1">
-      <c r="A3" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="13" t="s">
+      <c r="F3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="48" customHeight="1">
+      <c r="A4" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="O3" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="48" customHeight="1">
-      <c r="A4" s="15" t="s">
+      <c r="B4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="24">
+      <c r="D4" s="23">
         <v>46178</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <f>G4-M4</f>
+        <v>1</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="48" customHeight="1">
+      <c r="A5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="21">
+        <v>46178</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4">
+      <c r="F5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="7">
         <v>1</v>
       </c>
-      <c r="I4" s="4">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4">
-        <v>0</v>
-      </c>
-      <c r="M4" s="4">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="48" customHeight="1">
-      <c r="A5" s="9" t="s">
+      <c r="H5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7">
+        <v>0</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0</v>
+      </c>
+      <c r="K5" s="7">
+        <v>0</v>
+      </c>
+      <c r="L5" s="7">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7">
+        <v>0</v>
+      </c>
+      <c r="N5" s="7">
+        <f>G5-M5</f>
+        <v>1</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="48" customHeight="1">
+      <c r="A6" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="22">
+      <c r="D6" s="21">
         <v>46178</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7">
+      <c r="F6" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="7">
         <v>1</v>
       </c>
-      <c r="I5" s="7">
-        <v>0</v>
-      </c>
-      <c r="J5" s="7">
-        <v>0</v>
-      </c>
-      <c r="K5" s="7">
-        <v>0</v>
-      </c>
-      <c r="L5" s="7">
-        <v>0</v>
-      </c>
-      <c r="M5" s="7">
-        <v>0</v>
-      </c>
-      <c r="N5" s="7">
-        <v>0</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="48" customHeight="1">
-      <c r="A6" s="9" t="s">
+      <c r="H6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="7">
+        <v>0</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7">
+        <v>0</v>
+      </c>
+      <c r="M6" s="7">
+        <v>0</v>
+      </c>
+      <c r="N6" s="7">
+        <f>G6-M6</f>
+        <v>1</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="48" customHeight="1">
+      <c r="A7" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C7" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="22">
+      <c r="D7" s="24">
         <v>46178</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7">
+      <c r="E7" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="10">
         <v>1</v>
       </c>
-      <c r="I6" s="7">
-        <v>0</v>
-      </c>
-      <c r="J6" s="7">
-        <v>0</v>
-      </c>
-      <c r="K6" s="7">
-        <v>0</v>
-      </c>
-      <c r="L6" s="7">
-        <v>0</v>
-      </c>
-      <c r="M6" s="7">
-        <v>0</v>
-      </c>
-      <c r="N6" s="7">
-        <v>0</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="48" customHeight="1">
-      <c r="A7" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="25">
-        <v>46178</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11">
+      <c r="H7" s="10">
+        <v>0</v>
+      </c>
+      <c r="I7" s="10">
+        <v>0</v>
+      </c>
+      <c r="J7" s="10">
+        <v>0</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10">
+        <v>0</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0</v>
+      </c>
+      <c r="N7" s="10">
+        <f>G7-M7</f>
         <v>1</v>
       </c>
-      <c r="I7" s="11">
-        <v>0</v>
-      </c>
-      <c r="J7" s="11">
-        <v>0</v>
-      </c>
-      <c r="K7" s="11">
-        <v>0</v>
-      </c>
-      <c r="L7" s="11">
-        <v>0</v>
-      </c>
-      <c r="M7" s="11">
-        <v>0</v>
-      </c>
-      <c r="N7" s="11">
-        <v>0</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>83</v>
+      <c r="O7" s="10" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:15">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joeyaj/Desktop/Woosong-Apply/Woosong-Apply/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062C3298-1587-BC4D-BA77-26A87DE1D6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FFAD60-CE25-CB4B-B0E1-7E84947CA060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1240" yWindow="660" windowWidth="29000" windowHeight="14040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1400" yWindow="660" windowWidth="28840" windowHeight="16840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Claude Log" sheetId="5" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="114">
   <si>
     <t>又松大学招生系统 - 使用说明</t>
   </si>
@@ -133,9 +133,6 @@
   </si>
   <si>
     <t>标入</t>
-  </si>
-  <si>
-    <t>入学</t>
   </si>
   <si>
     <t>备注</t>
@@ -355,6 +352,38 @@
   </si>
   <si>
     <t>三表入学列已改为动态公式，随取消列自动重算。</t>
+  </si>
+  <si>
+    <t>询问每周如何下prompt更新data表，并确认data表是动态表的分类统计。</t>
+  </si>
+  <si>
+    <t>解释更新流程并提供prompt模板</t>
+  </si>
+  <si>
+    <t>确认data=动态表按维度分组汇总。说明无需指定起始行，上传整张动态表即可重算。提供了完整版与最简版prompt模板。</t>
+  </si>
+  <si>
+    <t>已答复；建议可将规则存为可复用技能。</t>
+  </si>
+  <si>
+    <t>用户确认取消统计规则=动态表取消列标☑的人数。</t>
+  </si>
+  <si>
+    <t>确认取消列统计规则</t>
+  </si>
+  <si>
+    <t>检查当前动态0605.xlsx发现尚无取消列(学部止于L标入/大学院N/SolBridge J)。约定:取消=组内取消列☑人数,入学=申请-取消(公式已就位)。</t>
+  </si>
+  <si>
+    <t>规则已确认;待用户上传含取消列的动态表后套用。当前取消仍为0。</t>
+  </si>
+  <si>
+    <t>预计入学</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>实际入学</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -613,11 +642,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -632,6 +656,11 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -847,107 +876,152 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738CB936-C75A-7447-9910-9C93B26D3435}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <cols>
+    <col min="3" max="3" width="103.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="256" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="C1" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="D1" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="E1" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="F1" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="21">
         <v>46178</v>
       </c>
       <c r="C2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" t="s">
         <v>86</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>87</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>88</v>
-      </c>
-      <c r="F2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="21">
         <v>46178</v>
       </c>
       <c r="C3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" t="s">
         <v>90</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>91</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>92</v>
-      </c>
-      <c r="F3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="21">
         <v>46178</v>
       </c>
       <c r="C4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" t="s">
         <v>94</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>95</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>96</v>
-      </c>
-      <c r="F4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="21">
         <v>46178</v>
       </c>
       <c r="C5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" t="s">
         <v>101</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>102</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>103</v>
       </c>
-      <c r="F5" t="s">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="21">
+        <v>46178</v>
+      </c>
+      <c r="C6" t="s">
         <v>104</v>
+      </c>
+      <c r="D6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="21">
+        <v>46178</v>
+      </c>
+      <c r="C7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F7" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -965,12 +1039,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
@@ -1038,8 +1112,8 @@
       </c>
     </row>
     <row r="20" spans="1:1" ht="15">
-      <c r="A20" s="22" t="s">
-        <v>73</v>
+      <c r="A20" s="17" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1068,7 +1142,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q49"/>
+  <dimension ref="A1:R49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10" hidden="1" customWidth="1"/>
@@ -1078,32 +1152,33 @@
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="6" width="32" customWidth="1"/>
     <col min="7" max="8" width="12" customWidth="1"/>
-    <col min="9" max="16" width="10" customWidth="1"/>
-    <col min="17" max="17" width="42" customWidth="1"/>
+    <col min="9" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="20">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:18" ht="20">
+      <c r="A1" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-    </row>
-    <row r="3" spans="1:17" ht="42.75" customHeight="1">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+    </row>
+    <row r="3" spans="1:18" ht="42.75" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>18</v>
       </c>
@@ -1147,39 +1222,42 @@
         <v>31</v>
       </c>
       <c r="O3" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P3" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="R3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="Q3" s="13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="48" customHeight="1">
+    </row>
+    <row r="4" spans="1:18" ht="48" customHeight="1">
       <c r="A4" s="2">
         <v>2026</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="23">
+        <v>40</v>
+      </c>
+      <c r="D4" s="18">
         <v>46178</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="I4" s="4">
         <v>4</v>
@@ -1203,37 +1281,38 @@
         <v>0</v>
       </c>
       <c r="P4" s="4">
-        <f>I4-O4</f>
+        <f t="shared" ref="P4:P17" si="0">I4-O4</f>
         <v>4</v>
       </c>
-      <c r="Q4" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="48" customHeight="1">
+      <c r="Q4" s="10"/>
+      <c r="R4" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="48" customHeight="1">
       <c r="A5" s="6">
         <v>2026</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="21">
+        <v>40</v>
+      </c>
+      <c r="D5" s="16">
         <v>46178</v>
       </c>
       <c r="E5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>48</v>
-      </c>
       <c r="H5" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I5" s="7">
         <v>1</v>
@@ -1257,35 +1336,36 @@
         <v>0</v>
       </c>
       <c r="P5" s="7">
-        <f>I5-O5</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q5" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="48" customHeight="1">
+      <c r="Q5" s="10"/>
+      <c r="R5" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="48" customHeight="1">
       <c r="A6" s="6"/>
       <c r="B6" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="21">
+        <v>40</v>
+      </c>
+      <c r="D6" s="16">
         <v>46178</v>
       </c>
       <c r="E6" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>47</v>
-      </c>
       <c r="G6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="I6" s="7">
         <v>3</v>
@@ -1309,35 +1389,36 @@
         <v>0</v>
       </c>
       <c r="P6" s="7">
-        <f>I6-O6</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="Q6" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="48" customHeight="1">
+      <c r="Q6" s="10"/>
+      <c r="R6" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="48" customHeight="1">
       <c r="A7" s="8"/>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="16">
+        <v>46178</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="21">
-        <v>46178</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="I7" s="7">
         <v>4</v>
@@ -1361,35 +1442,36 @@
         <v>0</v>
       </c>
       <c r="P7" s="7">
-        <f>I7-O7</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="Q7" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="48" customHeight="1">
+      <c r="Q7" s="10"/>
+      <c r="R7" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="48" customHeight="1">
       <c r="A8" s="8"/>
       <c r="B8" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="21">
+        <v>40</v>
+      </c>
+      <c r="D8" s="16">
         <v>46178</v>
       </c>
       <c r="E8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>54</v>
-      </c>
       <c r="G8" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I8" s="7">
         <v>1</v>
@@ -1413,35 +1495,36 @@
         <v>0</v>
       </c>
       <c r="P8" s="7">
-        <f>I8-O8</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q8" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1">
+      <c r="Q8" s="10"/>
+      <c r="R8" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="48" customHeight="1">
       <c r="A9" s="8"/>
       <c r="B9" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="21">
+        <v>40</v>
+      </c>
+      <c r="D9" s="16">
         <v>46178</v>
       </c>
       <c r="E9" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>59</v>
-      </c>
       <c r="G9" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I9" s="7">
         <v>1</v>
@@ -1465,35 +1548,36 @@
         <v>0</v>
       </c>
       <c r="P9" s="7">
-        <f>I9-O9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q9" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="48" customHeight="1">
+      <c r="Q9" s="10"/>
+      <c r="R9" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="48" customHeight="1">
       <c r="A10" s="8"/>
       <c r="B10" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="21">
+        <v>40</v>
+      </c>
+      <c r="D10" s="16">
         <v>46178</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>49</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>50</v>
       </c>
       <c r="I10" s="7">
         <v>1</v>
@@ -1517,35 +1601,36 @@
         <v>0</v>
       </c>
       <c r="P10" s="7">
-        <f>I10-O10</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q10" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="48" customHeight="1">
+      <c r="Q10" s="10"/>
+      <c r="R10" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="48" customHeight="1">
       <c r="A11" s="8"/>
       <c r="B11" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="21">
+        <v>40</v>
+      </c>
+      <c r="D11" s="16">
         <v>46178</v>
       </c>
       <c r="E11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>57</v>
-      </c>
       <c r="G11" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I11" s="7">
         <v>1</v>
@@ -1569,35 +1654,36 @@
         <v>0</v>
       </c>
       <c r="P11" s="7">
-        <f>I11-O11</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q11" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="48" customHeight="1">
+      <c r="Q11" s="10"/>
+      <c r="R11" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="48" customHeight="1">
       <c r="A12" s="8"/>
       <c r="B12" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="21">
+        <v>40</v>
+      </c>
+      <c r="D12" s="16">
         <v>46178</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I12" s="7">
         <v>1</v>
@@ -1621,35 +1707,36 @@
         <v>0</v>
       </c>
       <c r="P12" s="7">
-        <f>I12-O12</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q12" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="48" customHeight="1">
+      <c r="Q12" s="10"/>
+      <c r="R12" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="48" customHeight="1">
       <c r="A13" s="8"/>
       <c r="B13" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="21">
+        <v>40</v>
+      </c>
+      <c r="D13" s="16">
         <v>46178</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="I13" s="7">
         <v>1</v>
@@ -1673,35 +1760,36 @@
         <v>0</v>
       </c>
       <c r="P13" s="7">
-        <f>I13-O13</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q13" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="48" customHeight="1">
+      <c r="Q13" s="10"/>
+      <c r="R13" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="48" customHeight="1">
       <c r="A14" s="9"/>
       <c r="B14" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="21">
+        <v>40</v>
+      </c>
+      <c r="D14" s="16">
         <v>46178</v>
       </c>
       <c r="E14" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>50</v>
       </c>
       <c r="I14" s="10">
         <v>3</v>
@@ -1725,35 +1813,36 @@
         <v>0</v>
       </c>
       <c r="P14" s="10">
-        <f>I14-O14</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="Q14" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="42">
+      <c r="Q14" s="10"/>
+      <c r="R14" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="42">
       <c r="A15" s="9"/>
       <c r="B15" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="21">
+        <v>40</v>
+      </c>
+      <c r="D15" s="16">
         <v>46178</v>
       </c>
       <c r="E15" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>79</v>
-      </c>
       <c r="G15" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I15" s="10">
         <v>1</v>
@@ -1777,35 +1866,36 @@
         <v>0</v>
       </c>
       <c r="P15" s="10">
-        <f>I15-O15</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q15" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="42">
+      <c r="Q15" s="10"/>
+      <c r="R15" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="42">
       <c r="A16" s="9"/>
       <c r="B16" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="21">
+        <v>40</v>
+      </c>
+      <c r="D16" s="16">
         <v>46178</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G16" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="I16" s="10">
         <v>3</v>
@@ -1829,35 +1919,36 @@
         <v>0</v>
       </c>
       <c r="P16" s="10">
-        <f>I16-O16</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="Q16" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="42">
+      <c r="Q16" s="10"/>
+      <c r="R16" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="42">
       <c r="A17" s="9"/>
       <c r="B17" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="21">
+        <v>40</v>
+      </c>
+      <c r="D17" s="16">
         <v>46178</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I17" s="10">
         <v>2</v>
@@ -1881,14 +1972,15 @@
         <v>0</v>
       </c>
       <c r="P17" s="10">
-        <f>I17-O17</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q17" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="Q17" s="10"/>
+      <c r="R17" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1906,8 +1998,9 @@
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="R18" s="1"/>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1925,8 +2018,9 @@
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="R19" s="1"/>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1944,8 +2038,9 @@
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="R20" s="1"/>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1963,8 +2058,9 @@
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="R21" s="1"/>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1982,8 +2078,9 @@
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
-    </row>
-    <row r="23" spans="1:17">
+      <c r="R22" s="1"/>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -2001,8 +2098,9 @@
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
-    </row>
-    <row r="24" spans="1:17">
+      <c r="R23" s="1"/>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -2020,8 +2118,9 @@
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
-    </row>
-    <row r="25" spans="1:17">
+      <c r="R24" s="1"/>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -2039,8 +2138,9 @@
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
-    </row>
-    <row r="26" spans="1:17">
+      <c r="R25" s="1"/>
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2058,8 +2158,9 @@
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
-    </row>
-    <row r="27" spans="1:17">
+      <c r="R26" s="1"/>
+    </row>
+    <row r="27" spans="1:18">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2077,8 +2178,9 @@
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
-    </row>
-    <row r="28" spans="1:17">
+      <c r="R27" s="1"/>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2096,8 +2198,9 @@
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
-    </row>
-    <row r="29" spans="1:17">
+      <c r="R28" s="1"/>
+    </row>
+    <row r="29" spans="1:18">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2115,8 +2218,9 @@
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
-    </row>
-    <row r="30" spans="1:17">
+      <c r="R29" s="1"/>
+    </row>
+    <row r="30" spans="1:18">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2134,8 +2238,9 @@
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
-    </row>
-    <row r="31" spans="1:17">
+      <c r="R30" s="1"/>
+    </row>
+    <row r="31" spans="1:18">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2153,8 +2258,9 @@
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
-    </row>
-    <row r="32" spans="1:17">
+      <c r="R31" s="1"/>
+    </row>
+    <row r="32" spans="1:18">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2172,8 +2278,9 @@
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
-    </row>
-    <row r="33" spans="1:17">
+      <c r="R32" s="1"/>
+    </row>
+    <row r="33" spans="1:18">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2191,8 +2298,9 @@
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
-    </row>
-    <row r="34" spans="1:17">
+      <c r="R33" s="1"/>
+    </row>
+    <row r="34" spans="1:18">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2210,8 +2318,9 @@
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
-    </row>
-    <row r="35" spans="1:17">
+      <c r="R34" s="1"/>
+    </row>
+    <row r="35" spans="1:18">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2229,8 +2338,9 @@
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
-    </row>
-    <row r="36" spans="1:17">
+      <c r="R35" s="1"/>
+    </row>
+    <row r="36" spans="1:18">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2248,8 +2358,9 @@
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
-    </row>
-    <row r="37" spans="1:17">
+      <c r="R36" s="1"/>
+    </row>
+    <row r="37" spans="1:18">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2267,8 +2378,9 @@
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
-    </row>
-    <row r="38" spans="1:17">
+      <c r="R37" s="1"/>
+    </row>
+    <row r="38" spans="1:18">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2286,8 +2398,9 @@
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
-    </row>
-    <row r="39" spans="1:17">
+      <c r="R38" s="1"/>
+    </row>
+    <row r="39" spans="1:18">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2305,8 +2418,9 @@
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
-    </row>
-    <row r="40" spans="1:17">
+      <c r="R39" s="1"/>
+    </row>
+    <row r="40" spans="1:18">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2324,8 +2438,9 @@
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
-    </row>
-    <row r="41" spans="1:17">
+      <c r="R40" s="1"/>
+    </row>
+    <row r="41" spans="1:18">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2343,8 +2458,9 @@
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
-    </row>
-    <row r="42" spans="1:17">
+      <c r="R41" s="1"/>
+    </row>
+    <row r="42" spans="1:18">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2362,8 +2478,9 @@
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
-    </row>
-    <row r="43" spans="1:17">
+      <c r="R42" s="1"/>
+    </row>
+    <row r="43" spans="1:18">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2381,8 +2498,9 @@
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
-    </row>
-    <row r="44" spans="1:17">
+      <c r="R43" s="1"/>
+    </row>
+    <row r="44" spans="1:18">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2400,8 +2518,9 @@
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
-    </row>
-    <row r="45" spans="1:17">
+      <c r="R44" s="1"/>
+    </row>
+    <row r="45" spans="1:18">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2419,8 +2538,9 @@
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
-    </row>
-    <row r="46" spans="1:17">
+      <c r="R45" s="1"/>
+    </row>
+    <row r="46" spans="1:18">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2438,8 +2558,9 @@
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
-    </row>
-    <row r="47" spans="1:17">
+      <c r="R46" s="1"/>
+    </row>
+    <row r="47" spans="1:18">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2457,8 +2578,9 @@
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
-    </row>
-    <row r="48" spans="1:17">
+      <c r="R47" s="1"/>
+    </row>
+    <row r="48" spans="1:18">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2476,8 +2598,9 @@
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
-    </row>
-    <row r="49" spans="1:17">
+      <c r="R48" s="1"/>
+    </row>
+    <row r="49" spans="1:18">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2495,10 +2618,11 @@
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2507,7 +2631,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Q49"/>
+  <dimension ref="A1:R49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10" hidden="1" customWidth="1"/>
@@ -2517,32 +2641,33 @@
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="42" customWidth="1"/>
     <col min="7" max="8" width="12" customWidth="1"/>
-    <col min="9" max="16" width="10" customWidth="1"/>
-    <col min="17" max="17" width="42" customWidth="1"/>
+    <col min="9" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="20">
-      <c r="A1" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-    </row>
-    <row r="3" spans="1:17" ht="42.75" customHeight="1">
+    <row r="1" spans="1:18" ht="20">
+      <c r="A1" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+    </row>
+    <row r="3" spans="1:18" ht="42.75" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>18</v>
       </c>
@@ -2559,10 +2684,10 @@
         <v>22</v>
       </c>
       <c r="F3" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="12" t="s">
         <v>35</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>36</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>25</v>
@@ -2586,39 +2711,42 @@
         <v>31</v>
       </c>
       <c r="O3" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P3" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="R3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="Q3" s="13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="48" customHeight="1">
+    </row>
+    <row r="4" spans="1:18" ht="48" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="21">
+        <v>40</v>
+      </c>
+      <c r="D4" s="16">
         <v>46178</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="H4" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I4" s="4">
         <v>3</v>
@@ -2645,34 +2773,35 @@
         <f>I4-O4</f>
         <v>3</v>
       </c>
-      <c r="Q4" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="48" customHeight="1">
+      <c r="Q4" s="10"/>
+      <c r="R4" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="48" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="21">
+        <v>40</v>
+      </c>
+      <c r="D5" s="16">
         <v>46178</v>
       </c>
       <c r="E5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>65</v>
-      </c>
       <c r="H5" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I5" s="7">
         <v>1</v>
@@ -2699,34 +2828,35 @@
         <f>I5-O5</f>
         <v>1</v>
       </c>
-      <c r="Q5" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="48" customHeight="1">
+      <c r="Q5" s="10"/>
+      <c r="R5" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="48" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="21">
+        <v>40</v>
+      </c>
+      <c r="D6" s="16">
         <v>46178</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I6" s="7">
         <v>1</v>
@@ -2753,34 +2883,35 @@
         <f>I6-O6</f>
         <v>1</v>
       </c>
-      <c r="Q6" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="48" customHeight="1">
+      <c r="Q6" s="10"/>
+      <c r="R6" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="48" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="24">
+        <v>40</v>
+      </c>
+      <c r="D7" s="19">
         <v>46178</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I7" s="10">
         <v>7</v>
@@ -2807,11 +2938,12 @@
         <f>I7-O7</f>
         <v>7</v>
       </c>
-      <c r="Q7" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -2829,8 +2961,9 @@
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8" s="1"/>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -2848,8 +2981,9 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9" s="1"/>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -2867,8 +3001,9 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10" s="1"/>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -2886,8 +3021,9 @@
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="R11" s="1"/>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -2905,8 +3041,9 @@
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12" s="1"/>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -2924,8 +3061,9 @@
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="R13" s="1"/>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -2943,8 +3081,9 @@
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="R14" s="1"/>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -2962,8 +3101,9 @@
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="R15" s="1"/>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -2981,8 +3121,9 @@
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="R16" s="1"/>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -3000,8 +3141,9 @@
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="R17" s="1"/>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -3019,8 +3161,9 @@
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="R18" s="1"/>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -3038,8 +3181,9 @@
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="R19" s="1"/>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -3057,8 +3201,9 @@
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="R20" s="1"/>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -3076,8 +3221,9 @@
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="R21" s="1"/>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -3095,8 +3241,9 @@
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
-    </row>
-    <row r="23" spans="1:17">
+      <c r="R22" s="1"/>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -3114,8 +3261,9 @@
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
-    </row>
-    <row r="24" spans="1:17">
+      <c r="R23" s="1"/>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -3133,8 +3281,9 @@
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
-    </row>
-    <row r="25" spans="1:17">
+      <c r="R24" s="1"/>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -3152,8 +3301,9 @@
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
-    </row>
-    <row r="26" spans="1:17">
+      <c r="R25" s="1"/>
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -3171,8 +3321,9 @@
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
-    </row>
-    <row r="27" spans="1:17">
+      <c r="R26" s="1"/>
+    </row>
+    <row r="27" spans="1:18">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -3190,8 +3341,9 @@
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
-    </row>
-    <row r="28" spans="1:17">
+      <c r="R27" s="1"/>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -3209,8 +3361,9 @@
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
-    </row>
-    <row r="29" spans="1:17">
+      <c r="R28" s="1"/>
+    </row>
+    <row r="29" spans="1:18">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -3228,8 +3381,9 @@
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
-    </row>
-    <row r="30" spans="1:17">
+      <c r="R29" s="1"/>
+    </row>
+    <row r="30" spans="1:18">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -3247,8 +3401,9 @@
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
-    </row>
-    <row r="31" spans="1:17">
+      <c r="R30" s="1"/>
+    </row>
+    <row r="31" spans="1:18">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -3266,8 +3421,9 @@
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
-    </row>
-    <row r="32" spans="1:17">
+      <c r="R31" s="1"/>
+    </row>
+    <row r="32" spans="1:18">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -3285,8 +3441,9 @@
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
-    </row>
-    <row r="33" spans="1:17">
+      <c r="R32" s="1"/>
+    </row>
+    <row r="33" spans="1:18">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -3304,8 +3461,9 @@
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
-    </row>
-    <row r="34" spans="1:17">
+      <c r="R33" s="1"/>
+    </row>
+    <row r="34" spans="1:18">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -3323,8 +3481,9 @@
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
-    </row>
-    <row r="35" spans="1:17">
+      <c r="R34" s="1"/>
+    </row>
+    <row r="35" spans="1:18">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -3342,8 +3501,9 @@
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
-    </row>
-    <row r="36" spans="1:17">
+      <c r="R35" s="1"/>
+    </row>
+    <row r="36" spans="1:18">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -3361,8 +3521,9 @@
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
-    </row>
-    <row r="37" spans="1:17">
+      <c r="R36" s="1"/>
+    </row>
+    <row r="37" spans="1:18">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -3380,8 +3541,9 @@
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
-    </row>
-    <row r="38" spans="1:17">
+      <c r="R37" s="1"/>
+    </row>
+    <row r="38" spans="1:18">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -3399,8 +3561,9 @@
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
-    </row>
-    <row r="39" spans="1:17">
+      <c r="R38" s="1"/>
+    </row>
+    <row r="39" spans="1:18">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -3418,8 +3581,9 @@
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
-    </row>
-    <row r="40" spans="1:17">
+      <c r="R39" s="1"/>
+    </row>
+    <row r="40" spans="1:18">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -3437,8 +3601,9 @@
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
-    </row>
-    <row r="41" spans="1:17">
+      <c r="R40" s="1"/>
+    </row>
+    <row r="41" spans="1:18">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -3456,8 +3621,9 @@
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
-    </row>
-    <row r="42" spans="1:17">
+      <c r="R41" s="1"/>
+    </row>
+    <row r="42" spans="1:18">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -3475,8 +3641,9 @@
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
-    </row>
-    <row r="43" spans="1:17">
+      <c r="R42" s="1"/>
+    </row>
+    <row r="43" spans="1:18">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -3494,8 +3661,9 @@
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
-    </row>
-    <row r="44" spans="1:17">
+      <c r="R43" s="1"/>
+    </row>
+    <row r="44" spans="1:18">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -3513,8 +3681,9 @@
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
-    </row>
-    <row r="45" spans="1:17">
+      <c r="R44" s="1"/>
+    </row>
+    <row r="45" spans="1:18">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -3532,8 +3701,9 @@
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
-    </row>
-    <row r="46" spans="1:17">
+      <c r="R45" s="1"/>
+    </row>
+    <row r="46" spans="1:18">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -3551,8 +3721,9 @@
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
-    </row>
-    <row r="47" spans="1:17">
+      <c r="R46" s="1"/>
+    </row>
+    <row r="47" spans="1:18">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -3570,8 +3741,9 @@
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
-    </row>
-    <row r="48" spans="1:17">
+      <c r="R47" s="1"/>
+    </row>
+    <row r="48" spans="1:18">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -3589,8 +3761,9 @@
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
-    </row>
-    <row r="49" spans="1:17">
+      <c r="R48" s="1"/>
+    </row>
+    <row r="49" spans="1:18">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -3608,10 +3781,11 @@
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3620,7 +3794,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3629,30 +3803,31 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="34" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="14" width="10" customWidth="1"/>
-    <col min="15" max="15" width="69.19921875" customWidth="1"/>
+    <col min="7" max="15" width="10" customWidth="1"/>
+    <col min="16" max="16" width="69.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-    </row>
-    <row r="3" spans="1:15" ht="42.75" customHeight="1">
+    <row r="1" spans="1:16" ht="20">
+      <c r="A1" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+    </row>
+    <row r="3" spans="1:16" ht="42.75" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>18</v>
       </c>
@@ -3666,7 +3841,7 @@
         <v>21</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>24</v>
@@ -3690,33 +3865,36 @@
         <v>31</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N3" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="O3" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="P3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="48" customHeight="1">
+    </row>
+    <row r="4" spans="1:16" ht="48" customHeight="1">
       <c r="A4" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="23">
+      <c r="D4" s="18">
         <v>46178</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G4" s="4">
         <v>1</v>
@@ -3743,28 +3921,29 @@
         <f>G4-M4</f>
         <v>1</v>
       </c>
-      <c r="O4" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="48" customHeight="1">
+      <c r="O4" s="10"/>
+      <c r="P4" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="48" customHeight="1">
       <c r="A5" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="21">
+      <c r="D5" s="16">
         <v>46178</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G5" s="7">
         <v>1</v>
@@ -3791,28 +3970,29 @@
         <f>G5-M5</f>
         <v>1</v>
       </c>
-      <c r="O5" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="48" customHeight="1">
+      <c r="O5" s="10"/>
+      <c r="P5" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="48" customHeight="1">
       <c r="A6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="21">
+      <c r="D6" s="16">
         <v>46178</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G6" s="7">
         <v>1</v>
@@ -3839,28 +4019,29 @@
         <f>G6-M6</f>
         <v>1</v>
       </c>
-      <c r="O6" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="48" customHeight="1">
+      <c r="O6" s="10"/>
+      <c r="P6" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="48" customHeight="1">
       <c r="A7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="C7" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="24">
+      <c r="D7" s="19">
         <v>46178</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7" s="10">
         <v>1</v>
@@ -3887,11 +4068,12 @@
         <f>G7-M7</f>
         <v>1</v>
       </c>
-      <c r="O7" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="O7" s="10"/>
+      <c r="P7" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -3907,8 +4089,9 @@
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -3924,8 +4107,9 @@
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -3941,8 +4125,9 @@
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -3958,8 +4143,9 @@
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -3975,8 +4161,9 @@
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -3992,8 +4179,9 @@
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -4009,8 +4197,9 @@
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -4026,8 +4215,9 @@
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -4043,8 +4233,9 @@
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -4060,8 +4251,9 @@
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -4077,8 +4269,9 @@
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -4094,8 +4287,9 @@
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -4111,8 +4305,9 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -4128,8 +4323,9 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -4145,8 +4341,9 @@
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -4162,8 +4359,9 @@
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
-    </row>
-    <row r="24" spans="1:15">
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -4179,8 +4377,9 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -4196,8 +4395,9 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -4213,8 +4413,9 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -4230,8 +4431,9 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -4247,8 +4449,9 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -4264,8 +4467,9 @@
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -4281,8 +4485,9 @@
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="1:15">
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -4298,8 +4503,9 @@
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="1:15">
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -4315,8 +4521,9 @@
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
-    </row>
-    <row r="33" spans="1:15">
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -4332,8 +4539,9 @@
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
-    </row>
-    <row r="34" spans="1:15">
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -4349,8 +4557,9 @@
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
-    </row>
-    <row r="35" spans="1:15">
+      <c r="P34" s="1"/>
+    </row>
+    <row r="35" spans="1:16">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -4366,8 +4575,9 @@
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
-    </row>
-    <row r="36" spans="1:15">
+      <c r="P35" s="1"/>
+    </row>
+    <row r="36" spans="1:16">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -4383,8 +4593,9 @@
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
-    </row>
-    <row r="37" spans="1:15">
+      <c r="P36" s="1"/>
+    </row>
+    <row r="37" spans="1:16">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -4400,8 +4611,9 @@
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
-    </row>
-    <row r="38" spans="1:15">
+      <c r="P37" s="1"/>
+    </row>
+    <row r="38" spans="1:16">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -4417,8 +4629,9 @@
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
-    </row>
-    <row r="39" spans="1:15">
+      <c r="P38" s="1"/>
+    </row>
+    <row r="39" spans="1:16">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -4434,8 +4647,9 @@
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
-    </row>
-    <row r="40" spans="1:15">
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" spans="1:16">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -4451,8 +4665,9 @@
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
-    </row>
-    <row r="41" spans="1:15">
+      <c r="P40" s="1"/>
+    </row>
+    <row r="41" spans="1:16">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -4468,8 +4683,9 @@
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
-    </row>
-    <row r="42" spans="1:15">
+      <c r="P41" s="1"/>
+    </row>
+    <row r="42" spans="1:16">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -4485,8 +4701,9 @@
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
-    </row>
-    <row r="43" spans="1:15">
+      <c r="P42" s="1"/>
+    </row>
+    <row r="43" spans="1:16">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -4502,8 +4719,9 @@
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
-    </row>
-    <row r="44" spans="1:15">
+      <c r="P43" s="1"/>
+    </row>
+    <row r="44" spans="1:16">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -4519,8 +4737,9 @@
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
-    </row>
-    <row r="45" spans="1:15">
+      <c r="P44" s="1"/>
+    </row>
+    <row r="45" spans="1:16">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -4536,8 +4755,9 @@
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
-    </row>
-    <row r="46" spans="1:15">
+      <c r="P45" s="1"/>
+    </row>
+    <row r="46" spans="1:16">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -4553,8 +4773,9 @@
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
-    </row>
-    <row r="47" spans="1:15">
+      <c r="P46" s="1"/>
+    </row>
+    <row r="47" spans="1:16">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -4570,8 +4791,9 @@
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="P47" s="1"/>
+    </row>
+    <row r="48" spans="1:16">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -4587,8 +4809,9 @@
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
-    </row>
-    <row r="49" spans="1:15">
+      <c r="P48" s="1"/>
+    </row>
+    <row r="49" spans="1:16">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -4604,10 +4827,11 @@
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joeyaj/Desktop/Woosong-Apply/Woosong-Apply/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FFAD60-CE25-CB4B-B0E1-7E84947CA060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06622653-2D96-554D-97CF-E16BBC5DDF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="660" windowWidth="28840" windowHeight="16840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1460" yWindow="660" windowWidth="28780" windowHeight="17460" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Claude Log" sheetId="5" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="【大学院】周报月报" sheetId="3" r:id="rId4"/>
     <sheet name="【SolBridge】周报月报" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="126">
   <si>
     <t>又松大学招生系统 - 使用说明</t>
   </si>
@@ -153,15 +152,9 @@
     <t>专业</t>
   </si>
   <si>
-    <t>2026</t>
-  </si>
-  <si>
     <t>2026-2 秋季学期</t>
   </si>
   <si>
-    <t>第23周</t>
-  </si>
-  <si>
     <t>College of Culinary Arts</t>
   </si>
   <si>
@@ -250,10 +243,6 @@
   </si>
   <si>
     <t>2026-2 学期</t>
-  </si>
-  <si>
-    <t>2026-2 学期</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">   - 缴费 = 学费缴纳</t>
@@ -338,10 +327,6 @@
     <t>询问数未在动态表中统计；面试按面试时间非空人数统计；取消无来源暂按0；入学=申请−取消。</t>
   </si>
   <si>
-    <t>询问数未在动态表中统计；源表无面试时间列，面试暂按0；取消无来源暂按0；入学=申请−取消。</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>三张表在标入后增加取消列，入学=申请-取消。</t>
   </si>
   <si>
@@ -384,13 +369,65 @@
   <si>
     <t>实际入学</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>컴퓨터공학전공</t>
+  </si>
+  <si>
+    <t>자유전공</t>
+  </si>
+  <si>
+    <t>컴퓨터·미디어융합학과 미디어·게임·영상융합전공(미디어·영상융합코스)</t>
+  </si>
+  <si>
+    <t>上传新动态表0605，调用 dongtai-weekly-report 技能刷新三张周报月报表。</t>
+  </si>
+  <si>
+    <t>读全表重新分组统计并重写三张目标表</t>
+  </si>
+  <si>
+    <t>学部据(学院,专业,类型,语言)分成16组(申请28)；大学院据(学院,学科,学位,语言)5组(申请14)；SolBridge据(专业,类型)4组(申请4)。面试=面试时间非空(学部12/大学院6/SB0)；取消无源=0，入学=申请-取消公式。基准日期2026-06-05第23周。注：首次copyToRange误覆盖E-O列，已逐行重写修复。</t>
+  </si>
+  <si>
+    <t>【学部】A4:R19、【大学院】A4:R8、【SolBridge】A4:P7已刷新；合计28/14/4与源表一致，无错误值。</t>
+  </si>
+  <si>
+    <t>截图显示大学院新增一名申请人（No.15 王博策 WANG BOCE），要求计入汇总。</t>
+  </si>
+  <si>
+    <t>将对应组申请人数+1</t>
+  </si>
+  <si>
+    <t>王博策=硕士/일반대학원/AI경영학과 AI경영학전공 AI경영학코스/한국어，归入现有组（行4）。截图无面试时间、各阶段未勾选，故仅申请+1，其余不变。</t>
+  </si>
+  <si>
+    <t>【大学院】I4 申请 8→9，预计入学随公式自动为9；大学院申请合计=15。</t>
+  </si>
+  <si>
+    <t>第24周</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>要求将三表所有行的周次按今天基准更新。</t>
+  </si>
+  <si>
+    <t>更新三表周次与基准日期</t>
+  </si>
+  <si>
+    <t>今天=2026-06-08，ISO第24周。将C列周次由「第23周」改为「第24周」，D列基准日期公式改为=DATE(2026,6,8)。范围：学部4-19、大学院4-8、SolBridge4-7。</t>
+  </si>
+  <si>
+    <t>三表数据行周次均为第24周，基准日期为2026-06-08。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -432,13 +469,6 @@
       <name val="Wawati TC"/>
       <family val="3"/>
       <charset val="136"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Batang"/>
-      <family val="1"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
@@ -484,7 +514,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -505,20 +535,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -597,7 +613,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -612,55 +628,38 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -876,7 +875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738CB936-C75A-7447-9910-9C93B26D3435}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="3" max="3" width="103.796875" bestFit="1" customWidth="1"/>
@@ -885,143 +884,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="E1" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="F1" s="12" t="s">
         <v>81</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="F1" s="20" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="13">
         <v>46178</v>
       </c>
       <c r="C2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" t="s">
         <v>85</v>
-      </c>
-      <c r="D2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="13">
         <v>46178</v>
       </c>
       <c r="C3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3" t="s">
         <v>89</v>
-      </c>
-      <c r="D3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="13">
         <v>46178</v>
       </c>
       <c r="C4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F4" t="s">
         <v>93</v>
-      </c>
-      <c r="D4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F4" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="13">
         <v>46178</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="13">
         <v>46178</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="13">
         <v>46178</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F7" t="s">
-        <v>111</v>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="21">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="C8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="21">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="C9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="21">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="C10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F10" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1039,12 +1101,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20">
-      <c r="A1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
@@ -1112,8 +1174,8 @@
       </c>
     </row>
     <row r="20" spans="1:1" ht="15">
-      <c r="A20" s="17" t="s">
-        <v>72</v>
+      <c r="A20" s="11" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1157,80 +1219,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="20">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="3" spans="1:18" ht="42.75" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="N3" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="P3" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q3" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="R3" s="13" t="s">
+      <c r="O3" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="R3" s="9" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1239,25 +1301,26 @@
         <v>2026</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="19">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="18">
-        <v>46178</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="H4" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I4" s="4">
         <v>4</v>
@@ -1281,744 +1344,853 @@
         <v>0</v>
       </c>
       <c r="P4" s="4">
-        <f t="shared" ref="P4:P17" si="0">I4-O4</f>
+        <f>I4-O4</f>
         <v>4</v>
       </c>
-      <c r="Q4" s="10"/>
+      <c r="Q4" s="6"/>
       <c r="R4" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="48" customHeight="1">
-      <c r="A5" s="6">
+      <c r="A5" s="2">
         <v>2026</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="19">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4">
+        <v>1</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <f>I5-O5</f>
+        <v>1</v>
+      </c>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="48" customHeight="1">
+      <c r="A6" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="19">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="4">
+        <v>3</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <f t="shared" ref="P6:P19" si="0">I6-O6</f>
+        <v>3</v>
+      </c>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="48" customHeight="1">
+      <c r="A7" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="19">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="16">
-        <v>46178</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" s="7">
+      <c r="G7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="4">
+        <v>4</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="48" customHeight="1">
+      <c r="A8" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" s="19">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="4">
         <v>1</v>
       </c>
-      <c r="J5" s="7">
-        <v>0</v>
-      </c>
-      <c r="K5" s="7">
-        <v>1</v>
-      </c>
-      <c r="L5" s="7">
-        <v>0</v>
-      </c>
-      <c r="M5" s="7">
-        <v>0</v>
-      </c>
-      <c r="N5" s="7">
-        <v>0</v>
-      </c>
-      <c r="O5" s="7">
-        <v>0</v>
-      </c>
-      <c r="P5" s="7">
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="48" customHeight="1">
-      <c r="A6" s="6"/>
-      <c r="B6" s="3" t="s">
+      <c r="Q8" s="6"/>
+      <c r="R8" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="48" customHeight="1">
+      <c r="A9" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="19">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1</v>
+      </c>
+      <c r="J9" s="4">
+        <v>1</v>
+      </c>
+      <c r="K9" s="4">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="48" customHeight="1">
+      <c r="A10" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="19">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1</v>
+      </c>
+      <c r="J10" s="4">
+        <v>1</v>
+      </c>
+      <c r="K10" s="4">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="48" customHeight="1">
+      <c r="A11" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" s="19">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1</v>
+      </c>
+      <c r="J11" s="4">
+        <v>1</v>
+      </c>
+      <c r="K11" s="4">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="48" customHeight="1">
+      <c r="A12" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="19">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1</v>
+      </c>
+      <c r="K12" s="4">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4">
+        <v>0</v>
+      </c>
+      <c r="P12" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="48" customHeight="1">
+      <c r="A13" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="19">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4">
+        <v>0</v>
+      </c>
+      <c r="P13" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="48" customHeight="1">
+      <c r="A14" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D14" s="19">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="16">
-        <v>46178</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" s="7">
+      <c r="G14" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I14" s="4">
         <v>3</v>
       </c>
-      <c r="J6" s="7">
-        <v>0</v>
-      </c>
-      <c r="K6" s="7">
-        <v>0</v>
-      </c>
-      <c r="L6" s="7">
-        <v>0</v>
-      </c>
-      <c r="M6" s="7">
-        <v>0</v>
-      </c>
-      <c r="N6" s="7">
-        <v>0</v>
-      </c>
-      <c r="O6" s="7">
-        <v>0</v>
-      </c>
-      <c r="P6" s="7">
+      <c r="J14" s="4">
+        <v>3</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="48" customHeight="1">
-      <c r="A7" s="8"/>
-      <c r="B7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="16">
-        <v>46178</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="7">
-        <v>4</v>
-      </c>
-      <c r="J7" s="7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="7">
-        <v>0</v>
-      </c>
-      <c r="L7" s="7">
-        <v>0</v>
-      </c>
-      <c r="M7" s="7">
-        <v>0</v>
-      </c>
-      <c r="N7" s="7">
-        <v>0</v>
-      </c>
-      <c r="O7" s="7">
-        <v>0</v>
-      </c>
-      <c r="P7" s="7">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="48" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="16">
-        <v>46178</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8" s="7">
+      <c r="Q14" s="6"/>
+      <c r="R14" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="42">
+      <c r="A15" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="19">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" s="4">
         <v>1</v>
       </c>
-      <c r="J8" s="7">
-        <v>0</v>
-      </c>
-      <c r="K8" s="7">
-        <v>0</v>
-      </c>
-      <c r="L8" s="7">
-        <v>0</v>
-      </c>
-      <c r="M8" s="7">
-        <v>0</v>
-      </c>
-      <c r="N8" s="7">
-        <v>0</v>
-      </c>
-      <c r="O8" s="7">
-        <v>0</v>
-      </c>
-      <c r="P8" s="7">
+      <c r="J15" s="4">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="48" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="16">
-        <v>46178</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="7" t="s">
+      <c r="Q15" s="6"/>
+      <c r="R15" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="42">
+      <c r="A16" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D16" s="19">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="7">
+      <c r="F16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" s="4">
+        <v>3</v>
+      </c>
+      <c r="J16" s="4">
         <v>1</v>
       </c>
-      <c r="J9" s="7">
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="42">
+      <c r="A17" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="19">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I17" s="4">
         <v>1</v>
       </c>
-      <c r="K9" s="7">
-        <v>0</v>
-      </c>
-      <c r="L9" s="7">
-        <v>0</v>
-      </c>
-      <c r="M9" s="7">
-        <v>0</v>
-      </c>
-      <c r="N9" s="7">
-        <v>0</v>
-      </c>
-      <c r="O9" s="7">
-        <v>0</v>
-      </c>
-      <c r="P9" s="7">
+      <c r="J17" s="4">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4">
+        <v>0</v>
+      </c>
+      <c r="M17" s="4">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4">
+        <v>0</v>
+      </c>
+      <c r="P17" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="48" customHeight="1">
-      <c r="A10" s="8"/>
-      <c r="B10" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="16">
-        <v>46178</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="7" t="s">
+      <c r="Q17" s="6"/>
+      <c r="R17" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="42">
+      <c r="A18" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="19">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="I10" s="7">
+      <c r="F18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I18" s="4">
         <v>1</v>
       </c>
-      <c r="J10" s="7">
-        <v>1</v>
-      </c>
-      <c r="K10" s="7">
-        <v>0</v>
-      </c>
-      <c r="L10" s="7">
-        <v>0</v>
-      </c>
-      <c r="M10" s="7">
-        <v>0</v>
-      </c>
-      <c r="N10" s="7">
-        <v>0</v>
-      </c>
-      <c r="O10" s="7">
-        <v>0</v>
-      </c>
-      <c r="P10" s="7">
+      <c r="J18" s="4">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4">
+        <v>0</v>
+      </c>
+      <c r="M18" s="4">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4">
+        <v>0</v>
+      </c>
+      <c r="P18" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="48" customHeight="1">
-      <c r="A11" s="8"/>
-      <c r="B11" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="16">
-        <v>46178</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="7" t="s">
+      <c r="Q18" s="6"/>
+      <c r="R18" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="42">
+      <c r="A19" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" s="19">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I11" s="7">
+      <c r="I19" s="4">
         <v>1</v>
       </c>
-      <c r="J11" s="7">
-        <v>1</v>
-      </c>
-      <c r="K11" s="7">
-        <v>0</v>
-      </c>
-      <c r="L11" s="7">
-        <v>0</v>
-      </c>
-      <c r="M11" s="7">
-        <v>0</v>
-      </c>
-      <c r="N11" s="7">
-        <v>0</v>
-      </c>
-      <c r="O11" s="7">
-        <v>0</v>
-      </c>
-      <c r="P11" s="7">
+      <c r="J19" s="4">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4">
+        <v>0</v>
+      </c>
+      <c r="M19" s="4">
+        <v>0</v>
+      </c>
+      <c r="N19" s="4">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4">
+        <v>0</v>
+      </c>
+      <c r="P19" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="48" customHeight="1">
-      <c r="A12" s="8"/>
-      <c r="B12" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="16">
-        <v>46178</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="7">
-        <v>1</v>
-      </c>
-      <c r="J12" s="7">
-        <v>1</v>
-      </c>
-      <c r="K12" s="7">
-        <v>0</v>
-      </c>
-      <c r="L12" s="7">
-        <v>0</v>
-      </c>
-      <c r="M12" s="7">
-        <v>0</v>
-      </c>
-      <c r="N12" s="7">
-        <v>0</v>
-      </c>
-      <c r="O12" s="7">
-        <v>0</v>
-      </c>
-      <c r="P12" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="48" customHeight="1">
-      <c r="A13" s="8"/>
-      <c r="B13" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="16">
-        <v>46178</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="I13" s="7">
-        <v>1</v>
-      </c>
-      <c r="J13" s="7">
-        <v>0</v>
-      </c>
-      <c r="K13" s="7">
-        <v>0</v>
-      </c>
-      <c r="L13" s="7">
-        <v>0</v>
-      </c>
-      <c r="M13" s="7">
-        <v>0</v>
-      </c>
-      <c r="N13" s="7">
-        <v>0</v>
-      </c>
-      <c r="O13" s="7">
-        <v>0</v>
-      </c>
-      <c r="P13" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="48" customHeight="1">
-      <c r="A14" s="9"/>
-      <c r="B14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="16">
-        <v>46178</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="I14" s="10">
-        <v>3</v>
-      </c>
-      <c r="J14" s="10">
-        <v>3</v>
-      </c>
-      <c r="K14" s="10">
-        <v>0</v>
-      </c>
-      <c r="L14" s="10">
-        <v>0</v>
-      </c>
-      <c r="M14" s="10">
-        <v>0</v>
-      </c>
-      <c r="N14" s="10">
-        <v>0</v>
-      </c>
-      <c r="O14" s="10">
-        <v>0</v>
-      </c>
-      <c r="P14" s="10">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="42">
-      <c r="A15" s="9"/>
-      <c r="B15" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="16">
-        <v>46178</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="I15" s="10">
-        <v>1</v>
-      </c>
-      <c r="J15" s="10">
-        <v>0</v>
-      </c>
-      <c r="K15" s="10">
-        <v>0</v>
-      </c>
-      <c r="L15" s="10">
-        <v>0</v>
-      </c>
-      <c r="M15" s="10">
-        <v>0</v>
-      </c>
-      <c r="N15" s="10">
-        <v>0</v>
-      </c>
-      <c r="O15" s="10">
-        <v>0</v>
-      </c>
-      <c r="P15" s="10">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="42">
-      <c r="A16" s="9"/>
-      <c r="B16" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="16">
-        <v>46178</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="I16" s="10">
-        <v>3</v>
-      </c>
-      <c r="J16" s="10">
-        <v>0</v>
-      </c>
-      <c r="K16" s="10">
-        <v>0</v>
-      </c>
-      <c r="L16" s="10">
-        <v>0</v>
-      </c>
-      <c r="M16" s="10">
-        <v>0</v>
-      </c>
-      <c r="N16" s="10">
-        <v>0</v>
-      </c>
-      <c r="O16" s="10">
-        <v>0</v>
-      </c>
-      <c r="P16" s="10">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="42">
-      <c r="A17" s="9"/>
-      <c r="B17" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="16">
-        <v>46178</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="I17" s="10">
-        <v>2</v>
-      </c>
-      <c r="J17" s="10">
-        <v>0</v>
-      </c>
-      <c r="K17" s="10">
-        <v>0</v>
-      </c>
-      <c r="L17" s="10">
-        <v>0</v>
-      </c>
-      <c r="M17" s="10">
-        <v>0</v>
-      </c>
-      <c r="N17" s="10">
-        <v>0</v>
-      </c>
-      <c r="O17" s="10">
-        <v>0</v>
-      </c>
-      <c r="P17" s="10">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
+      <c r="Q19" s="6"/>
+      <c r="R19" s="5" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="1"/>
@@ -2646,113 +2818,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="20">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="3" spans="1:18" ht="42.75" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="N3" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="P3" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q3" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="R3" s="13" t="s">
+      <c r="O3" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="R3" s="9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="48" customHeight="1">
-      <c r="A4" s="14" t="s">
-        <v>38</v>
+      <c r="A4" s="10">
+        <v>2026</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="16">
-        <v>46178</v>
+        <v>121</v>
+      </c>
+      <c r="D4" s="20">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>61</v>
-      </c>
       <c r="H4" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I4" s="4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J4" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K4" s="4">
         <v>0</v>
@@ -2771,197 +2944,236 @@
       </c>
       <c r="P4" s="4">
         <f>I4-O4</f>
-        <v>3</v>
-      </c>
-      <c r="Q4" s="10"/>
+        <v>9</v>
+      </c>
+      <c r="Q4" s="6"/>
       <c r="R4" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="48" customHeight="1">
-      <c r="A5" s="8" t="s">
-        <v>38</v>
+      <c r="A5" s="10">
+        <v>2026</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="16">
-        <v>46178</v>
-      </c>
-      <c r="E5" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="20">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" s="7">
+      <c r="H5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="4">
         <v>1</v>
       </c>
-      <c r="J5" s="7">
-        <v>0</v>
-      </c>
-      <c r="K5" s="7">
-        <v>0</v>
-      </c>
-      <c r="L5" s="7">
-        <v>0</v>
-      </c>
-      <c r="M5" s="7">
-        <v>0</v>
-      </c>
-      <c r="N5" s="7">
-        <v>0</v>
-      </c>
-      <c r="O5" s="7">
-        <v>0</v>
-      </c>
-      <c r="P5" s="7">
+      <c r="J5" s="4">
+        <v>1</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
         <f>I5-O5</f>
         <v>1</v>
       </c>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="7" t="s">
-        <v>99</v>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="4" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="48" customHeight="1">
-      <c r="A6" s="8" t="s">
-        <v>38</v>
+      <c r="A6" s="10">
+        <v>2026</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="16">
-        <v>46178</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" s="7">
+        <v>68</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="20">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="4">
+        <v>3</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <f t="shared" ref="P6:P8" si="0">I6-O6</f>
+        <v>3</v>
+      </c>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="48" customHeight="1">
+      <c r="A7" s="10">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="20">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="4">
         <v>1</v>
       </c>
-      <c r="J6" s="7">
-        <v>0</v>
-      </c>
-      <c r="K6" s="7">
-        <v>0</v>
-      </c>
-      <c r="L6" s="7">
-        <v>0</v>
-      </c>
-      <c r="M6" s="7">
-        <v>0</v>
-      </c>
-      <c r="N6" s="7">
-        <v>0</v>
-      </c>
-      <c r="O6" s="7">
-        <v>0</v>
-      </c>
-      <c r="P6" s="7">
-        <f>I6-O6</f>
+      <c r="J7" s="4">
         <v>1</v>
       </c>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="48" customHeight="1">
-      <c r="A7" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="19">
-        <v>46178</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="I7" s="10">
-        <v>7</v>
-      </c>
-      <c r="J7" s="10">
-        <v>0</v>
-      </c>
-      <c r="K7" s="10">
-        <v>0</v>
-      </c>
-      <c r="L7" s="10">
-        <v>0</v>
-      </c>
-      <c r="M7" s="10">
-        <v>0</v>
-      </c>
-      <c r="N7" s="10">
-        <v>0</v>
-      </c>
-      <c r="O7" s="10">
-        <v>0</v>
-      </c>
-      <c r="P7" s="10">
-        <f>I7-O7</f>
-        <v>7</v>
-      </c>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="42">
+      <c r="A8" s="10">
+        <v>2026</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" s="20">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="4" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1"/>
@@ -3808,93 +4020,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="20">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
     </row>
     <row r="3" spans="1:16" ht="42.75" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="N3" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="O3" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="P3" s="13" t="s">
+      <c r="M3" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="P3" s="9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="48" customHeight="1">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="10">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="C4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="18">
-        <v>46178</v>
+        <v>121</v>
+      </c>
+      <c r="D4" s="19">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G4" s="4">
         <v>1</v>
@@ -3921,156 +4134,159 @@
         <f>G4-M4</f>
         <v>1</v>
       </c>
-      <c r="O4" s="10"/>
+      <c r="O4" s="6"/>
       <c r="P4" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="48" customHeight="1">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="10">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="16">
-        <v>46178</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5" s="7">
+      <c r="C5" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="19">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="4">
         <v>1</v>
       </c>
-      <c r="H5" s="7">
-        <v>0</v>
-      </c>
-      <c r="I5" s="7">
-        <v>0</v>
-      </c>
-      <c r="J5" s="7">
-        <v>0</v>
-      </c>
-      <c r="K5" s="7">
-        <v>0</v>
-      </c>
-      <c r="L5" s="7">
-        <v>0</v>
-      </c>
-      <c r="M5" s="7">
-        <v>0</v>
-      </c>
-      <c r="N5" s="7">
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
         <f>G5-M5</f>
         <v>1</v>
       </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="7" t="s">
-        <v>99</v>
+      <c r="O5" s="6"/>
+      <c r="P5" s="4" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="48" customHeight="1">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="10">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="16">
-        <v>46178</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="7">
+      <c r="C6" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="19">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="4">
         <v>1</v>
       </c>
-      <c r="H6" s="7">
-        <v>0</v>
-      </c>
-      <c r="I6" s="7">
-        <v>0</v>
-      </c>
-      <c r="J6" s="7">
-        <v>0</v>
-      </c>
-      <c r="K6" s="7">
-        <v>0</v>
-      </c>
-      <c r="L6" s="7">
-        <v>0</v>
-      </c>
-      <c r="M6" s="7">
-        <v>0</v>
-      </c>
-      <c r="N6" s="7">
-        <f>G6-M6</f>
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <f t="shared" ref="N6:N7" si="0">G6-M6</f>
         <v>1</v>
       </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="7" t="s">
-        <v>99</v>
+      <c r="O6" s="6"/>
+      <c r="P6" s="4" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="48" customHeight="1">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="10">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>40</v>
+      <c r="C7" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="D7" s="19">
-        <v>46178</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" s="10">
+        <f>DATE(2026,6,8)</f>
+        <v>46181</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="4">
         <v>1</v>
       </c>
-      <c r="H7" s="10">
-        <v>0</v>
-      </c>
-      <c r="I7" s="10">
-        <v>0</v>
-      </c>
-      <c r="J7" s="10">
-        <v>0</v>
-      </c>
-      <c r="K7" s="10">
-        <v>0</v>
-      </c>
-      <c r="L7" s="10">
-        <v>0</v>
-      </c>
-      <c r="M7" s="10">
-        <v>0</v>
-      </c>
-      <c r="N7" s="10">
-        <f>G7-M7</f>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10" t="s">
-        <v>99</v>
+      <c r="O7" s="6"/>
+      <c r="P7" s="4" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:16">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joeyaj/Desktop/Woosong-Apply/Woosong-Apply/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06622653-2D96-554D-97CF-E16BBC5DDF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C21026-2E19-7348-A4D2-56C83074FFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1460" yWindow="660" windowWidth="28780" windowHeight="17460" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1660" yWindow="660" windowWidth="28580" windowHeight="15800" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Claude Log" sheetId="5" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="【大学院】周报月报" sheetId="3" r:id="rId4"/>
     <sheet name="【SolBridge】周报月报" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,6 +28,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="129">
   <si>
     <t>又松大学招生系统 - 使用说明</t>
   </si>
@@ -155,24 +156,12 @@
     <t>2026-2 秋季学期</t>
   </si>
   <si>
-    <t>College of Culinary Arts</t>
-  </si>
-  <si>
-    <t>Global Culinary Arts</t>
-  </si>
-  <si>
     <t>교환</t>
   </si>
   <si>
     <t>영어</t>
   </si>
   <si>
-    <t>College of Software Convergence</t>
-  </si>
-  <si>
-    <t>Global Media &amp; Communication Arts</t>
-  </si>
-  <si>
     <t>신입</t>
   </si>
   <si>
@@ -188,12 +177,6 @@
     <t>未填写</t>
   </si>
   <si>
-    <t>JW Kim College of Future Studies</t>
-  </si>
-  <si>
-    <t>Global Interdisciplinary Studies (HADI)</t>
-  </si>
-  <si>
     <t>소프트웨어융합대학</t>
   </si>
   <si>
@@ -221,16 +204,7 @@
     <t>일반대학원</t>
   </si>
   <si>
-    <t>AI경영학과 AI경영학전공  Management Studies</t>
-  </si>
-  <si>
     <t>博士</t>
-  </si>
-  <si>
-    <t>AI경영학과 AI경영학전공 AI경영학_영어트랙</t>
-  </si>
-  <si>
-    <t>AI경영학과 AI경영학전공 AI경영학코스</t>
   </si>
   <si>
     <t>BBA</t>
@@ -324,9 +298,6 @@
     <t>取消</t>
   </si>
   <si>
-    <t>询问数未在动态表中统计；面试按面试时间非空人数统计；取消无来源暂按0；入学=申请−取消。</t>
-  </si>
-  <si>
     <t>三张表在标入后增加取消列，入学=申请-取消。</t>
   </si>
   <si>
@@ -404,20 +375,58 @@
     <t>【大学院】I4 申请 8→9，预计入学随公式自动为9；大学院申请合计=15。</t>
   </si>
   <si>
+    <t>要求将三表所有行的周次按今天基准更新。</t>
+  </si>
+  <si>
+    <t>更新三表周次与基准日期</t>
+  </si>
+  <si>
+    <t>今天=2026-06-08，ISO第24周。将C列周次由「第23周」改为「第24周」，D列基准日期公式改为=DATE(2026,6,8)。范围：学部4-19、大学院4-8、SolBridge4-7。</t>
+  </si>
+  <si>
+    <t>三表数据行周次均为第24周，基准日期为2026-06-08。</t>
+  </si>
+  <si>
     <t>第24周</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>要求将三表所有行的周次按今天基准更新。</t>
-  </si>
-  <si>
-    <t>更新三表周次与基准日期</t>
-  </si>
-  <si>
-    <t>今天=2026-06-08，ISO第24周。将C列周次由「第23周」改为「第24周」，D列基准日期公式改为=DATE(2026,6,8)。范围：学部4-19、大学院4-8、SolBridge4-7。</t>
-  </si>
-  <si>
-    <t>三表数据行周次均为第24周，基准日期为2026-06-08。</t>
+  </si>
+  <si>
+    <t>询问数未在动态表中统计；面试按面试时间非空人数统计；入学=申请−取消。</t>
+  </si>
+  <si>
+    <t>외식조리대학</t>
+  </si>
+  <si>
+    <t>글로벌조리전공</t>
+  </si>
+  <si>
+    <t>JCFS미래대학</t>
+  </si>
+  <si>
+    <t>휴먼디지털인터페이스(HADI)</t>
+  </si>
+  <si>
+    <t>AI경영학과 AI경영전공 AI경영학코스</t>
+  </si>
+  <si>
+    <t>AI경영학과 AI경영전공  Management Studies</t>
+  </si>
+  <si>
+    <t>AI경영학과 AI경영전공 AI경영학_영어트랙</t>
+  </si>
+  <si>
+    <t>AI경영학과 AI경영전공 철도경영학코스</t>
+  </si>
+  <si>
+    <t>上传动态0612.xlsx，调用 /dongtai-weekly-report刷新三张周报月报表，周次与基准日期按今天。</t>
+  </si>
+  <si>
+    <t>读全表重新分组统计并覆写三张目标表</t>
+  </si>
+  <si>
+    <t>动态表：学部32人/大学院18人/SolBridge 4人。学部戕6组、5组、大学院77组、SolBridge 4组。取消按动态表M列(SolBridge J)☑统计均=0。基准日期=DATE(2026,6,12)，周次=第24周(ISO)。</t>
+  </si>
+  <si>
+    <t>【学部】A4:R18、【大学院】A4:R10、【SolBridge】A4:P7 已刷新；申请合计 32/18/4 与源表一致，预计入学公式求值正确。</t>
   </si>
 </sst>
 </file>
@@ -648,11 +657,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -660,6 +664,11 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -875,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738CB936-C75A-7447-9910-9C93B26D3435}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="3" max="3" width="103.796875" bestFit="1" customWidth="1"/>
@@ -885,22 +894,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="12" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -911,16 +920,16 @@
         <v>46178</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F2" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -931,16 +940,16 @@
         <v>46178</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -951,16 +960,16 @@
         <v>46178</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="F4" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -971,16 +980,16 @@
         <v>46178</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="F5" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -991,16 +1000,16 @@
         <v>46178</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F6" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1011,79 +1020,100 @@
         <v>46178</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="F7" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="16">
         <f>DATE(2026,6,8)</f>
         <v>46181</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="F8" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="16">
         <f>DATE(2026,6,8)</f>
         <v>46181</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="F9" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="16">
         <f>DATE(2026,6,8)</f>
         <v>46181</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="F10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="16">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
+      </c>
+      <c r="C11" t="s">
         <v>125</v>
+      </c>
+      <c r="D11" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -1101,12 +1131,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
@@ -1175,7 +1205,7 @@
     </row>
     <row r="20" spans="1:1" ht="15">
       <c r="A20" s="11" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1219,26 +1249,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="20">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
     </row>
     <row r="3" spans="1:18" ht="42.75" customHeight="1">
       <c r="A3" s="7" t="s">
@@ -1284,13 +1314,13 @@
         <v>31</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="R3" s="9" t="s">
         <v>32</v>
@@ -1301,32 +1331,32 @@
         <v>2026</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D4" s="14">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I4" s="4">
         <v>4</v>
       </c>
       <c r="J4" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K4" s="4">
         <v>0</v>
@@ -1349,7 +1379,7 @@
       </c>
       <c r="Q4" s="6"/>
       <c r="R4" s="5" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="48" customHeight="1">
@@ -1357,32 +1387,32 @@
         <v>2026</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D5" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D5" s="14">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I5" s="4">
         <v>1</v>
       </c>
       <c r="J5" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="4">
         <v>1</v>
@@ -1405,7 +1435,7 @@
       </c>
       <c r="Q5" s="6"/>
       <c r="R5" s="5" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="48" customHeight="1">
@@ -1413,35 +1443,35 @@
         <v>2026</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D6" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D6" s="14">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I6" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="4">
         <v>0</v>
@@ -1456,12 +1486,12 @@
         <v>0</v>
       </c>
       <c r="P6" s="4">
-        <f t="shared" ref="P6:P19" si="0">I6-O6</f>
-        <v>3</v>
+        <f>I6-O6</f>
+        <v>4</v>
       </c>
       <c r="Q6" s="6"/>
       <c r="R6" s="5" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="48" customHeight="1">
@@ -1469,35 +1499,35 @@
         <v>2026</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D7" s="14">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="I7" s="4">
         <v>4</v>
       </c>
       <c r="J7" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K7" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L7" s="4">
         <v>0</v>
@@ -1512,12 +1542,12 @@
         <v>0</v>
       </c>
       <c r="P7" s="4">
-        <f t="shared" si="0"/>
+        <f>I7-O7</f>
         <v>4</v>
       </c>
       <c r="Q7" s="6"/>
       <c r="R7" s="5" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="48" customHeight="1">
@@ -1525,26 +1555,26 @@
         <v>2026</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D8" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D8" s="14">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I8" s="4">
         <v>1</v>
@@ -1568,12 +1598,12 @@
         <v>0</v>
       </c>
       <c r="P8" s="4">
-        <f t="shared" si="0"/>
+        <f>I8-O8</f>
         <v>1</v>
       </c>
       <c r="Q8" s="6"/>
       <c r="R8" s="5" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="48" customHeight="1">
@@ -1581,26 +1611,26 @@
         <v>2026</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D9" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D9" s="14">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I9" s="4">
         <v>1</v>
@@ -1624,12 +1654,12 @@
         <v>0</v>
       </c>
       <c r="P9" s="4">
-        <f t="shared" si="0"/>
+        <f>I9-O9</f>
         <v>1</v>
       </c>
       <c r="Q9" s="6"/>
       <c r="R9" s="5" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="48" customHeight="1">
@@ -1637,26 +1667,26 @@
         <v>2026</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D10" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D10" s="14">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I10" s="4">
         <v>1</v>
@@ -1680,12 +1710,12 @@
         <v>0</v>
       </c>
       <c r="P10" s="4">
-        <f t="shared" si="0"/>
+        <f>I10-O10</f>
         <v>1</v>
       </c>
       <c r="Q10" s="6"/>
       <c r="R10" s="5" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="48" customHeight="1">
@@ -1693,26 +1723,26 @@
         <v>2026</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D11" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D11" s="14">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
@@ -1721,7 +1751,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="4">
         <v>0</v>
@@ -1736,12 +1766,12 @@
         <v>0</v>
       </c>
       <c r="P11" s="4">
-        <f t="shared" si="0"/>
+        <f>I11-O11</f>
         <v>1</v>
       </c>
       <c r="Q11" s="6"/>
       <c r="R11" s="5" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="48" customHeight="1">
@@ -1749,32 +1779,32 @@
         <v>2026</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D12" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D12" s="14">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>
       </c>
       <c r="J12" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="4">
         <v>0</v>
@@ -1792,12 +1822,12 @@
         <v>0</v>
       </c>
       <c r="P12" s="4">
-        <f t="shared" si="0"/>
+        <f>I12-O12</f>
         <v>1</v>
       </c>
       <c r="Q12" s="6"/>
       <c r="R12" s="5" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="48" customHeight="1">
@@ -1805,35 +1835,35 @@
         <v>2026</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D13" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D13" s="14">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I13" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J13" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K13" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L13" s="4">
         <v>0</v>
@@ -1848,12 +1878,12 @@
         <v>0</v>
       </c>
       <c r="P13" s="4">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>I13-O13</f>
+        <v>3</v>
       </c>
       <c r="Q13" s="6"/>
       <c r="R13" s="5" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="48" customHeight="1">
@@ -1861,32 +1891,32 @@
         <v>2026</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D14" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D14" s="14">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I14" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K14" s="4">
         <v>0</v>
@@ -1904,46 +1934,46 @@
         <v>0</v>
       </c>
       <c r="P14" s="4">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>I14-O14</f>
+        <v>1</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="42">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="28">
       <c r="A15" s="2">
         <v>2026</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D15" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D15" s="14">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I15" s="4">
+        <v>3</v>
+      </c>
+      <c r="J15" s="4">
         <v>1</v>
       </c>
-      <c r="J15" s="4">
-        <v>0</v>
-      </c>
       <c r="K15" s="4">
         <v>0</v>
       </c>
@@ -1960,98 +1990,98 @@
         <v>0</v>
       </c>
       <c r="P15" s="4">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>I15-O15</f>
+        <v>3</v>
       </c>
       <c r="Q15" s="6"/>
       <c r="R15" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="42">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="28">
       <c r="A16" s="2">
         <v>2026</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D16" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D16" s="14">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I16" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J16" s="4">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4">
+        <f>I16-O16</f>
         <v>1</v>
-      </c>
-      <c r="K16" s="4">
-        <v>0</v>
-      </c>
-      <c r="L16" s="4">
-        <v>0</v>
-      </c>
-      <c r="M16" s="4">
-        <v>0</v>
-      </c>
-      <c r="N16" s="4">
-        <v>0</v>
-      </c>
-      <c r="O16" s="4">
-        <v>0</v>
-      </c>
-      <c r="P16" s="4">
-        <f t="shared" si="0"/>
-        <v>3</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="42">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="28">
       <c r="A17" s="2">
         <v>2026</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D17" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D17" s="14">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I17" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J17" s="4">
         <v>0</v>
@@ -2072,39 +2102,39 @@
         <v>0</v>
       </c>
       <c r="P17" s="4">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>I17-O17</f>
+        <v>5</v>
       </c>
       <c r="Q17" s="6"/>
       <c r="R17" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="42">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="28">
       <c r="A18" s="2">
         <v>2026</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D18" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D18" s="14">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I18" s="4">
         <v>1</v>
@@ -2128,69 +2158,33 @@
         <v>0</v>
       </c>
       <c r="P18" s="4">
-        <f t="shared" si="0"/>
+        <f>I18-O18</f>
         <v>1</v>
       </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="42">
-      <c r="A19" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D19" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I19" s="4">
-        <v>1</v>
-      </c>
-      <c r="J19" s="4">
-        <v>0</v>
-      </c>
-      <c r="K19" s="4">
-        <v>0</v>
-      </c>
-      <c r="L19" s="4">
-        <v>0</v>
-      </c>
-      <c r="M19" s="4">
-        <v>0</v>
-      </c>
-      <c r="N19" s="4">
-        <v>0</v>
-      </c>
-      <c r="O19" s="4">
-        <v>0</v>
-      </c>
-      <c r="P19" s="4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
       <c r="Q19" s="6"/>
-      <c r="R19" s="5" t="s">
-        <v>95</v>
-      </c>
+      <c r="R19" s="5"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="1"/>
@@ -2809,7 +2803,7 @@
     <col min="1" max="1" width="10" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="42" customWidth="1"/>
     <col min="7" max="8" width="12" customWidth="1"/>
@@ -2818,26 +2812,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="20">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
     </row>
     <row r="3" spans="1:18" ht="42.75" customHeight="1">
       <c r="A3" s="7" t="s">
@@ -2883,13 +2877,13 @@
         <v>31</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="R3" s="9" t="s">
         <v>32</v>
@@ -2900,29 +2894,29 @@
         <v>2026</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" s="15">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D4" s="20">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>64</v>
-      </c>
       <c r="G4" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I4" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4" s="4">
         <v>4</v>
@@ -2944,11 +2938,11 @@
       </c>
       <c r="P4" s="4">
         <f>I4-O4</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="R4" s="4" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="48" customHeight="1">
@@ -2956,26 +2950,26 @@
         <v>2026</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D5" s="20">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D5" s="15">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I5" s="4">
         <v>1</v>
@@ -3004,7 +2998,7 @@
       </c>
       <c r="Q5" s="6"/>
       <c r="R5" s="4" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="48" customHeight="1">
@@ -3012,26 +3006,26 @@
         <v>2026</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D6" s="20">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D6" s="15">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I6" s="4">
         <v>3</v>
@@ -3055,12 +3049,12 @@
         <v>0</v>
       </c>
       <c r="P6" s="4">
-        <f t="shared" ref="P6:P8" si="0">I6-O6</f>
+        <f>I6-O6</f>
         <v>3</v>
       </c>
       <c r="Q6" s="6"/>
       <c r="R6" s="4" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="48" customHeight="1">
@@ -3068,26 +3062,26 @@
         <v>2026</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" s="20">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D7" s="15">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I7" s="4">
         <v>1</v>
@@ -3111,42 +3105,42 @@
         <v>0</v>
       </c>
       <c r="P7" s="4">
-        <f t="shared" si="0"/>
+        <f>I7-O7</f>
         <v>1</v>
       </c>
       <c r="Q7" s="6"/>
       <c r="R7" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="42">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="28">
       <c r="A8" s="10">
         <v>2026</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D8" s="20">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D8" s="15">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I8" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="4">
         <v>0</v>
@@ -3167,53 +3161,125 @@
         <v>0</v>
       </c>
       <c r="P8" s="4">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>I8-O8</f>
+        <v>2</v>
       </c>
       <c r="Q8" s="6"/>
       <c r="R8" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="28">
+      <c r="A9" s="10">
+        <v>2026</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" s="15">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="4">
+        <v>2</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4">
+        <f>I9-O9</f>
+        <v>2</v>
+      </c>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="28">
+      <c r="A10" s="10">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="15">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4">
+        <f>I10-O10</f>
+        <v>1</v>
+      </c>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="4" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="1"/>
@@ -4020,24 +4086,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="20">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
     </row>
     <row r="3" spans="1:16" ht="42.75" customHeight="1">
       <c r="A3" s="7" t="s">
@@ -4077,13 +4143,13 @@
         <v>31</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="P3" s="9" t="s">
         <v>32</v>
@@ -4097,17 +4163,17 @@
         <v>38</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D4" s="14">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G4" s="4">
         <v>1</v>
@@ -4136,7 +4202,7 @@
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="4" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="48" customHeight="1">
@@ -4147,17 +4213,17 @@
         <v>38</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D5" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D5" s="14">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G5" s="4">
         <v>1</v>
@@ -4186,7 +4252,7 @@
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="4" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="48" customHeight="1">
@@ -4197,17 +4263,17 @@
         <v>38</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D6" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D6" s="14">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G6" s="4">
         <v>1</v>
@@ -4231,12 +4297,12 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <f t="shared" ref="N6:N7" si="0">G6-M6</f>
+        <f>G6-M6</f>
         <v>1</v>
       </c>
       <c r="O6" s="6"/>
       <c r="P6" s="4" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="48" customHeight="1">
@@ -4247,17 +4313,17 @@
         <v>38</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" s="19">
-        <f>DATE(2026,6,8)</f>
-        <v>46181</v>
+        <v>115</v>
+      </c>
+      <c r="D7" s="14">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G7" s="4">
         <v>1</v>
@@ -4281,12 +4347,12 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <f t="shared" si="0"/>
+        <f>G7-M7</f>
         <v>1</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="4" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:16">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joeyaj/Desktop/Woosong-Apply/Woosong-Apply/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C21026-2E19-7348-A4D2-56C83074FFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88431D24-3EF9-774A-AA4E-A6E83DFE7AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1660" yWindow="660" windowWidth="28580" windowHeight="15800" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4420" yWindow="660" windowWidth="25820" windowHeight="15800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Claude Log" sheetId="5" r:id="rId1"/>
@@ -1337,7 +1337,7 @@
         <v>115</v>
       </c>
       <c r="D4" s="14">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" ref="D4:D18" si="0">DATE(2026,6,12)</f>
         <v>46185</v>
       </c>
       <c r="E4" s="4" t="s">
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="4">
-        <f>I4-O4</f>
+        <f t="shared" ref="P4:P18" si="1">I4-O4</f>
         <v>4</v>
       </c>
       <c r="Q4" s="6"/>
@@ -1393,7 +1393,7 @@
         <v>115</v>
       </c>
       <c r="D5" s="14">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E5" s="4" t="s">
@@ -1430,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="4">
-        <f>I5-O5</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q5" s="6"/>
@@ -1449,7 +1449,7 @@
         <v>115</v>
       </c>
       <c r="D6" s="14">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E6" s="4" t="s">
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="4">
-        <f>I6-O6</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="Q6" s="6"/>
@@ -1505,7 +1505,7 @@
         <v>115</v>
       </c>
       <c r="D7" s="14">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E7" s="4" t="s">
@@ -1542,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="4">
-        <f>I7-O7</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="Q7" s="6"/>
@@ -1561,7 +1561,7 @@
         <v>115</v>
       </c>
       <c r="D8" s="14">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E8" s="4" t="s">
@@ -1598,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="4">
-        <f>I8-O8</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q8" s="6"/>
@@ -1617,7 +1617,7 @@
         <v>115</v>
       </c>
       <c r="D9" s="14">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E9" s="4" t="s">
@@ -1654,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="4">
-        <f>I9-O9</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q9" s="6"/>
@@ -1673,7 +1673,7 @@
         <v>115</v>
       </c>
       <c r="D10" s="14">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E10" s="4" t="s">
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="4">
-        <f>I10-O10</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q10" s="6"/>
@@ -1729,7 +1729,7 @@
         <v>115</v>
       </c>
       <c r="D11" s="14">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E11" s="4" t="s">
@@ -1766,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="4">
-        <f>I11-O11</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q11" s="6"/>
@@ -1785,7 +1785,7 @@
         <v>115</v>
       </c>
       <c r="D12" s="14">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E12" s="4" t="s">
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="4">
-        <f>I12-O12</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q12" s="6"/>
@@ -1841,7 +1841,7 @@
         <v>115</v>
       </c>
       <c r="D13" s="14">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E13" s="4" t="s">
@@ -1878,7 +1878,7 @@
         <v>0</v>
       </c>
       <c r="P13" s="4">
-        <f>I13-O13</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="Q13" s="6"/>
@@ -1897,7 +1897,7 @@
         <v>115</v>
       </c>
       <c r="D14" s="14">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E14" s="4" t="s">
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="4">
-        <f>I14-O14</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q14" s="6"/>
@@ -1953,7 +1953,7 @@
         <v>115</v>
       </c>
       <c r="D15" s="14">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E15" s="4" t="s">
@@ -1990,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="P15" s="4">
-        <f>I15-O15</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="Q15" s="6"/>
@@ -2009,7 +2009,7 @@
         <v>115</v>
       </c>
       <c r="D16" s="14">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="P16" s="4">
-        <f>I16-O16</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q16" s="6"/>
@@ -2065,7 +2065,7 @@
         <v>115</v>
       </c>
       <c r="D17" s="14">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E17" s="4" t="s">
@@ -2102,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="P17" s="4">
-        <f>I17-O17</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="Q17" s="6"/>
@@ -2121,7 +2121,7 @@
         <v>115</v>
       </c>
       <c r="D18" s="14">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E18" s="4" t="s">
@@ -2158,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="4">
-        <f>I18-O18</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q18" s="6"/>
@@ -2900,7 +2900,7 @@
         <v>115</v>
       </c>
       <c r="D4" s="15">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" ref="D4:D10" si="0">DATE(2026,6,12)</f>
         <v>46185</v>
       </c>
       <c r="E4" s="4" t="s">
@@ -2937,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="4">
-        <f>I4-O4</f>
+        <f t="shared" ref="P4:P10" si="1">I4-O4</f>
         <v>8</v>
       </c>
       <c r="Q4" s="6"/>
@@ -2956,7 +2956,7 @@
         <v>115</v>
       </c>
       <c r="D5" s="15">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E5" s="4" t="s">
@@ -2993,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="4">
-        <f>I5-O5</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q5" s="6"/>
@@ -3012,7 +3012,7 @@
         <v>115</v>
       </c>
       <c r="D6" s="15">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E6" s="4" t="s">
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="4">
-        <f>I6-O6</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="Q6" s="6"/>
@@ -3068,7 +3068,7 @@
         <v>115</v>
       </c>
       <c r="D7" s="15">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E7" s="4" t="s">
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="4">
-        <f>I7-O7</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q7" s="6"/>
@@ -3124,7 +3124,7 @@
         <v>115</v>
       </c>
       <c r="D8" s="15">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E8" s="4" t="s">
@@ -3161,7 +3161,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="4">
-        <f>I8-O8</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="Q8" s="6"/>
@@ -3180,7 +3180,7 @@
         <v>115</v>
       </c>
       <c r="D9" s="15">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E9" s="4" t="s">
@@ -3217,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="4">
-        <f>I9-O9</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="Q9" s="6"/>
@@ -3236,7 +3236,7 @@
         <v>115</v>
       </c>
       <c r="D10" s="15">
-        <f>DATE(2026,6,12)</f>
+        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="E10" s="4" t="s">
@@ -3273,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="4">
-        <f>I10-O10</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q10" s="6"/>
@@ -4176,10 +4176,10 @@
         <v>41</v>
       </c>
       <c r="G4" s="4">
+        <v>4</v>
+      </c>
+      <c r="H4" s="4">
         <v>1</v>
-      </c>
-      <c r="H4" s="4">
-        <v>0</v>
       </c>
       <c r="I4" s="4">
         <v>0</v>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="N4" s="4">
         <f>G4-M4</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="4" t="s">
@@ -4226,7 +4226,7 @@
         <v>39</v>
       </c>
       <c r="G5" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5" s="4">
         <v>0</v>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="N5" s="4">
         <f>G5-M5</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="4" t="s">
@@ -4276,7 +4276,7 @@
         <v>41</v>
       </c>
       <c r="G6" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="4">
         <v>0</v>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="N6" s="4">
         <f>G6-M6</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O6" s="6"/>
       <c r="P6" s="4" t="s">
@@ -4326,7 +4326,7 @@
         <v>45</v>
       </c>
       <c r="G7" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="4">
         <v>0</v>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="N7" s="4">
         <f>G7-M7</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="4" t="s">
